--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -815,7 +815,7 @@
         <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>2916</v>
+        <v>2914</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>29</v>
       </c>
       <c r="F27" t="n">
-        <v>8249</v>
+        <v>8247</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>84</v>
       </c>
       <c r="F69" t="n">
-        <v>16076</v>
+        <v>16064</v>
       </c>
       <c r="G69" t="n">
         <v>5209.32</v>
@@ -2523,7 +2523,7 @@
         <v>81</v>
       </c>
       <c r="F75" t="n">
-        <v>19314</v>
+        <v>19312</v>
       </c>
       <c r="G75" t="n">
         <v>8132.2</v>
@@ -3587,7 +3587,7 @@
         <v>3</v>
       </c>
       <c r="F113" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>10</v>
       </c>
       <c r="F117" t="n">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="G117" t="n">
         <v>1651.7</v>
@@ -4287,7 +4287,7 @@
         <v>4</v>
       </c>
       <c r="F138" t="n">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>248</v>
       </c>
       <c r="F171" t="n">
-        <v>30617</v>
+        <v>30614</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -2218,10 +2218,10 @@
         <v>14316</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2246,10 +2246,10 @@
         <v>7113</v>
       </c>
       <c r="G65" t="n">
-        <v>10167.8</v>
+        <v>15251.7</v>
       </c>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,12 +464,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_ST-01_ST-02_ST-03_HV_Phrase &amp; Broad</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -479,7 +479,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -497,17 +497,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>77.61</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>716</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -525,17 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -548,7 +548,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
+          <t>Nex_HnK_SP_KT_ST-01_ST-02_ST-03_HV_Phrase &amp; Broad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>181.48</v>
+        <v>17.07</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>926</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -576,50 +576,50 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
+          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>225.32</v>
+        <v>2284.47</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>1620</v>
+        <v>14131</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>10168.64</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
+          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>111.67</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2251</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -632,22 +632,22 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>118.35</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2185</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -660,22 +660,22 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>730.88</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>870</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -688,22 +688,22 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>535.47</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>4440</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -716,22 +716,22 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P- Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>460.72</v>
+        <v>663.16</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>6852</v>
+        <v>9398</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -744,12 +744,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -772,78 +772,78 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1458.01</v>
+        <v>490.32</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>29057</v>
+        <v>7026</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1244.92</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>265.04</v>
+        <v>2046.63</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>2914</v>
+        <v>2490</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5090.68</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1017.06</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5565</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -856,50 +856,50 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT - SP</t>
+          <t>Nexlev - B0DCK7ZH5P- Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>539.28</v>
+        <v>2467.99</v>
       </c>
       <c r="E16" t="n">
-        <v>28</v>
+        <v>354</v>
       </c>
       <c r="F16" t="n">
-        <v>2089</v>
+        <v>30260</v>
       </c>
       <c r="G16" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT -SP</t>
+          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>98.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -912,134 +912,134 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>6865.62</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>119888</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>12709.33</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>901.05</v>
+        <v>3032.48</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="F19" t="n">
-        <v>20181</v>
+        <v>43729</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5168.64</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>574.48</v>
+        <v>4447.2</v>
       </c>
       <c r="E20" t="n">
-        <v>33</v>
+        <v>295</v>
       </c>
       <c r="F20" t="n">
-        <v>5177</v>
+        <v>23077</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>20335.6</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(1)</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT - SP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>251.57</v>
+        <v>2415.76</v>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="F21" t="n">
-        <v>4926</v>
+        <v>11707</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>15251.7</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(2)</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT -SP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60.01</v>
+        <v>510.2</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>1854</v>
+        <v>3762</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1052,22 +1052,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - AT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,78 +1080,78 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - PT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>37.39</v>
+        <v>4171.96</v>
       </c>
       <c r="E24" t="n">
+        <v>291</v>
+      </c>
+      <c r="F24" t="n">
+        <v>105090</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12622.05</v>
+      </c>
+      <c r="H24" t="n">
         <v>6</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1341</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - PT(1)</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.37</v>
+        <v>3234.86</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="F25" t="n">
-        <v>532</v>
+        <v>45586</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>10589</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - Phrase</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(1)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>143.48</v>
+        <v>822.59</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="F26" t="n">
-        <v>2142</v>
+        <v>17688</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,22 +1164,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - AT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(2)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>257.02</v>
+        <v>370.16</v>
       </c>
       <c r="E27" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
-        <v>8247</v>
+        <v>6747</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,50 +1192,50 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - PT</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - AT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>33.4</v>
+        <v>1045.3</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="F28" t="n">
-        <v>1400</v>
+        <v>1944</v>
       </c>
       <c r="G28" t="n">
-        <v>11863.56</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>22.92</v>
+        <v>360.29</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="F29" t="n">
-        <v>1059</v>
+        <v>7581</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,22 +1248,22 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier- PT</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - PT(1)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.9</v>
+        <v>185.43</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>140</v>
+        <v>2643</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1276,22 +1276,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28.12</v>
+        <v>359.86</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F31" t="n">
-        <v>354</v>
+        <v>6794</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1304,22 +1304,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - AT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1153.72</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>31660</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1332,50 +1332,50 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>122.18</v>
+        <v>179.22</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>85</v>
+        <v>4361</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>11863.56</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>507.94</v>
+        <v>355.02</v>
       </c>
       <c r="E34" t="n">
         <v>34</v>
       </c>
       <c r="F34" t="n">
-        <v>776</v>
+        <v>12762</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1388,50 +1388,50 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier- PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1913.55</v>
+        <v>12.9</v>
       </c>
       <c r="E35" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>2742</v>
+        <v>673</v>
       </c>
       <c r="G35" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>100.27</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1228</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,12 +1444,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1472,22 +1472,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>168.66</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1425</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1500,22 +1500,22 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - AT</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>334.04</v>
+        <v>211.33</v>
       </c>
       <c r="E39" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>4466</v>
+        <v>264</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,68 +1528,68 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - CT</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>300.37</v>
+        <v>1773.53</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="F40" t="n">
-        <v>1702</v>
+        <v>3687</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>379.06</v>
+        <v>8613.4</v>
       </c>
       <c r="E41" t="n">
-        <v>22</v>
+        <v>337</v>
       </c>
       <c r="F41" t="n">
-        <v>3725</v>
+        <v>10393</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>20335.6</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,50 +1612,50 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - PT</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>23.17</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>5253.39</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>572.4</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>4612</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,50 +1668,50 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - AT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2400.78</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>41622</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>6184.75</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - CT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>245.22</v>
+        <v>1483.81</v>
       </c>
       <c r="E46" t="n">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="F46" t="n">
-        <v>2951</v>
+        <v>9811</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,22 +1724,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>876.84</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>5658</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1752,22 +1752,22 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>403.25</v>
+        <v>23.6</v>
       </c>
       <c r="E48" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>1349</v>
+        <v>1609</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,78 +1780,78 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT-Refine</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>507.95</v>
+        <v>61.11</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>1775</v>
+        <v>131</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>5253.39</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-PT</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>758.51</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>2101</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>91.34999999999999</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,50 +1864,50 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4903.05</v>
+        <v>1225.65</v>
       </c>
       <c r="E52" t="n">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="F52" t="n">
-        <v>46388</v>
+        <v>12848</v>
       </c>
       <c r="G52" t="n">
-        <v>12540.68</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>53.53</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1920,50 +1920,50 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>254.49</v>
+        <v>3417.66</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>256</v>
       </c>
       <c r="F54" t="n">
-        <v>2579</v>
+        <v>12024</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT-Refine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2322.44</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="F55" t="n">
-        <v>25</v>
+        <v>7432</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1976,50 +1976,50 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>357.42</v>
+        <v>3781.32</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>283</v>
       </c>
       <c r="F56" t="n">
-        <v>5885</v>
+        <v>9184</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>7963.570000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>458.62</v>
+        <v>162.04</v>
       </c>
       <c r="E57" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F57" t="n">
-        <v>3907</v>
+        <v>780</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2032,50 +2032,50 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>16189.88</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>146034</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>18811.02</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Sofa Cleaning Machine-SP-PT</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>163.46</v>
+        <v>206.05</v>
       </c>
       <c r="E59" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>637</v>
+        <v>949</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,50 +2088,50 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1195.52</v>
+        <v>755.5599999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="F60" t="n">
-        <v>10346</v>
+        <v>12378</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2093.33</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>9.870000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2144,50 +2144,50 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>342.68</v>
+        <v>1222.32</v>
       </c>
       <c r="E62" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F62" t="n">
-        <v>4783</v>
+        <v>24883</v>
       </c>
       <c r="G62" t="n">
-        <v>3426.67</v>
+        <v>4319.51</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-AT</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>116.58</v>
+        <v>802.79</v>
       </c>
       <c r="E63" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F63" t="n">
-        <v>2336</v>
+        <v>7291</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,106 +2200,106 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1499.02</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>14316</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2013.81</v>
+        <v>6.14</v>
       </c>
       <c r="E65" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>7113</v>
+        <v>26</v>
       </c>
       <c r="G65" t="n">
-        <v>15251.7</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1517.76</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>8720</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>1439.83</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop cleaner-SP-PT</t>
+          <t>Nexlev-B0DCK7ZH5P-Sofa Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>118.75</v>
+        <v>482.84</v>
       </c>
       <c r="E67" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F67" t="n">
-        <v>543</v>
+        <v>2293</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,78 +2312,78 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>380.23</v>
+        <v>1758.59</v>
       </c>
       <c r="E68" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F68" t="n">
-        <v>5303</v>
+        <v>13066</v>
       </c>
       <c r="G68" t="n">
-        <v>1736.44</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>856.63</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>16064</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>5209.32</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1989.25</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>75375</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2396,50 +2396,50 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1001.32</v>
+        <v>1437.63</v>
       </c>
       <c r="E71" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="F71" t="n">
-        <v>14260</v>
+        <v>21525</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>6853.34</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-AT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1488.12</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>31182</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2452,81 +2452,81 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>7456.45</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>77859</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1180.78</v>
+        <v>9073.959999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>104</v>
+        <v>399</v>
       </c>
       <c r="F74" t="n">
-        <v>59664</v>
+        <v>32827</v>
       </c>
       <c r="G74" t="n">
-        <v>2033.05</v>
+        <v>20335.6</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>940.87</v>
+        <v>4790.49</v>
       </c>
       <c r="E75" t="n">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="F75" t="n">
-        <v>19312</v>
+        <v>13102</v>
       </c>
       <c r="G75" t="n">
-        <v>8132.2</v>
+        <v>16691.53</v>
       </c>
       <c r="H75" t="n">
         <v>4</v>
@@ -2536,22 +2536,22 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-BM</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>152</v>
+        <v>719.1800000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F76" t="n">
-        <v>419</v>
+        <v>5406</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,152 +2564,152 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-PT</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>312.19</v>
+        <v>1255.86</v>
       </c>
       <c r="E77" t="n">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="F77" t="n">
-        <v>679</v>
+        <v>17502</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>5209.32</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>78.99000000000001</v>
+        <v>3528.79</v>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>337</v>
       </c>
       <c r="F78" t="n">
-        <v>460</v>
+        <v>71501</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>12155.08</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>51.64</v>
+        <v>10727.98</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>870</v>
       </c>
       <c r="F79" t="n">
-        <v>1813</v>
+        <v>460217</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>30503.4</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>678.7</v>
+        <v>4140.73</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>233</v>
       </c>
       <c r="F80" t="n">
-        <v>3552</v>
+        <v>54179</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>15251.7</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>498.9</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>12219</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2732,78 +2732,78 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>4201.41</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="F83" t="n">
-        <v>63</v>
+        <v>240634</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>6268.650000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>2929.5</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="F84" t="n">
-        <v>67</v>
+        <v>91072</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>10250</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-BM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1101.18</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>4361</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2816,22 +2816,22 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1313.94</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F86" t="n">
-        <v>14</v>
+        <v>3123</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2844,22 +2844,22 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7.61</v>
+        <v>626.14</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="F87" t="n">
-        <v>63</v>
+        <v>2662</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,22 +2872,22 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>527.3399999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F88" t="n">
-        <v>41</v>
+        <v>9161</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2900,56 +2900,56 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7.92</v>
+        <v>2221.04</v>
       </c>
       <c r="E89" t="n">
+        <v>135</v>
+      </c>
+      <c r="F89" t="n">
+        <v>14562</v>
+      </c>
+      <c r="G89" t="n">
+        <v>3304.24</v>
+      </c>
+      <c r="H89" t="n">
         <v>1</v>
-      </c>
-      <c r="F89" t="n">
-        <v>30</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>16.18</v>
+        <v>2267.86</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="F90" t="n">
-        <v>153</v>
+        <v>28083</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>6608.48</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>17</v>
+        <v>553</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3027,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>197</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3045,17 +3045,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>19.76</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3073,17 +3073,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>24.91</v>
+        <v>6.67</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>8.16</v>
+        <v>52.51</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F96" t="n">
-        <v>122</v>
+        <v>319</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3157,17 +3157,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F98" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3185,17 +3185,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>67.55</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F99" t="n">
-        <v>13</v>
+        <v>728</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3213,17 +3213,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7.77</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3269,17 +3269,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0F74DJYG6</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>8.17</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3353,17 +3353,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>75.28</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F105" t="n">
-        <v>91</v>
+        <v>390</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3409,45 +3409,45 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>43.09</v>
+        <v>22.12</v>
       </c>
       <c r="E107" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
-        <v>480</v>
+        <v>558</v>
       </c>
       <c r="G107" t="n">
-        <v>8466.1</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1406</v>
+        <v>63</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3460,12 +3460,12 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3488,12 +3488,12 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3516,22 +3516,22 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>7.77</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>133</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3544,22 +3544,22 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>11.21</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>66</v>
+        <v>1314</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3572,50 +3572,50 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.5</v>
+        <v>5.43</v>
       </c>
       <c r="E113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F113" t="n">
-        <v>196</v>
+        <v>40</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>931.36</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0F74DJYG6</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>7.07</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>386</v>
+        <v>213</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3628,12 +3628,12 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>907</v>
+        <v>170</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3656,22 +3656,22 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>122</v>
+        <v>274</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3684,40 +3684,40 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>34.46</v>
+        <v>44.13</v>
       </c>
       <c r="E117" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F117" t="n">
-        <v>2553</v>
+        <v>478</v>
       </c>
       <c r="G117" t="n">
-        <v>1651.7</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3727,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3740,50 +3740,50 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.71</v>
+        <v>138.84</v>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F119" t="n">
-        <v>317</v>
+        <v>3927</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>39.82</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>3270</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3796,22 +3796,22 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>17.66</v>
+        <v>4.91</v>
       </c>
       <c r="E121" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>929</v>
+        <v>344</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3824,22 +3824,22 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>42.66</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>1448</v>
+        <v>6</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3852,12 +3852,12 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3885,17 +3885,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>229</v>
+        <v>303</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3913,17 +3913,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>18.74</v>
+        <v>34.7</v>
       </c>
       <c r="E125" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F125" t="n">
-        <v>1890</v>
+        <v>1088</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3941,17 +3941,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>32.42</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1613</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3969,23 +3969,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>27.11</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F127" t="n">
-        <v>48</v>
+        <v>4746</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>761.86</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -3997,17 +3997,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>47</v>
+        <v>592</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4053,23 +4053,23 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7.02</v>
+        <v>198.83</v>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="F130" t="n">
-        <v>95</v>
+        <v>14496</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>4955.09</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4081,17 +4081,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3.8</v>
+        <v>14.13</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F131" t="n">
-        <v>29</v>
+        <v>370</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4109,17 +4109,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3.8</v>
+        <v>36.21</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F132" t="n">
-        <v>84</v>
+        <v>1291</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -4193,17 +4193,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F135" t="n">
-        <v>142</v>
+        <v>5149</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4221,17 +4221,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0F74DJYG6</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>14.83</v>
+        <v>185.02</v>
       </c>
       <c r="E136" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F136" t="n">
-        <v>358</v>
+        <v>5503</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4277,17 +4277,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>14.29</v>
+        <v>11.37</v>
       </c>
       <c r="E138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F138" t="n">
-        <v>954</v>
+        <v>192</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4305,17 +4305,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3.78</v>
+        <v>24.78</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F139" t="n">
-        <v>81</v>
+        <v>894</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4333,17 +4333,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>44.75</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>1425</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4356,22 +4356,22 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>75.38999999999999</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>12455</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4412,12 +4412,12 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4440,22 +4440,22 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4468,12 +4468,12 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>295</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4524,12 +4524,12 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -4539,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4552,22 +4552,22 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>399</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4580,22 +4580,22 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>7.54</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F149" t="n">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4608,50 +4608,50 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>14.45</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F150" t="n">
-        <v>4</v>
+        <v>406</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>12540.68</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>29.8</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>1117</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4664,12 +4664,12 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4692,12 +4692,12 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -4707,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>578</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4720,22 +4720,22 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0F74DJYG6</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>14.83</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F154" t="n">
-        <v>6</v>
+        <v>372</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4748,12 +4748,12 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>13</v>
+        <v>980</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4776,50 +4776,50 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5.7</v>
+        <v>44.36</v>
       </c>
       <c r="E156" t="n">
+        <v>13</v>
+      </c>
+      <c r="F156" t="n">
+        <v>3623</v>
+      </c>
+      <c r="G156" t="n">
+        <v>677.12</v>
+      </c>
+      <c r="H156" t="n">
         <v>1</v>
-      </c>
-      <c r="F156" t="n">
-        <v>46</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4832,22 +4832,22 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>13.89</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4860,50 +4860,50 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>148.64</v>
+        <v>227.77</v>
       </c>
       <c r="E159" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F159" t="n">
-        <v>1162</v>
+        <v>9063</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>350.93</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>4071</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4916,12 +4916,12 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4944,50 +4944,50 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1113.13</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>27515</v>
+        <v>28</v>
       </c>
       <c r="G162" t="n">
-        <v>3557.62</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>630.65</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>5445</v>
+        <v>46</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5000,22 +5000,22 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(1)</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>69.41</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>520</v>
+        <v>386</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5028,22 +5028,22 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(2)</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>177.68</v>
+        <v>5.7</v>
       </c>
       <c r="E165" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>622</v>
+        <v>22</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5056,22 +5056,22 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5084,40 +5084,40 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>28.44</v>
+        <v>5.28</v>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="G167" t="n">
-        <v>1244.92</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -5140,22 +5140,22 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>635.15</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>1693</v>
+        <v>23</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -5168,12 +5168,12 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -5183,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5196,22 +5196,22 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>970.12</v>
+        <v>3.62</v>
       </c>
       <c r="E171" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>30614</v>
+        <v>5</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -5224,22 +5224,22 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>148.61</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>722</v>
+        <v>105</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5252,40 +5252,40 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>962.71</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>16335</v>
+        <v>5</v>
       </c>
       <c r="G173" t="n">
-        <v>4066.1</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B08L46ZKKZ</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -5295,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -5308,12 +5308,12 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0FNQS4RRD</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -5323,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -5336,50 +5336,50 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>990.1</v>
+        <v>1.64</v>
       </c>
       <c r="E176" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F176" t="n">
-        <v>20147</v>
+        <v>40</v>
       </c>
       <c r="G176" t="n">
-        <v>10116.96</v>
+        <v>233.05</v>
       </c>
       <c r="H176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>126.07</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>725</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5392,22 +5392,22 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>45.59</v>
+        <v>17.1</v>
       </c>
       <c r="E178" t="n">
         <v>3</v>
       </c>
       <c r="F178" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5420,22 +5420,22 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT01</t>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>245.23</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>1406</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5448,22 +5448,22 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>94.59</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F180" t="n">
-        <v>0</v>
+        <v>702</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5476,22 +5476,22 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>956.9299999999999</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>2798</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5504,12 +5504,12 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -5532,22 +5532,22 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>694.58</v>
+        <v>747.55</v>
       </c>
       <c r="E183" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F183" t="n">
-        <v>24470</v>
+        <v>6629</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5560,50 +5560,50 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-PT-SP</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>157.6</v>
+        <v>1290.98</v>
       </c>
       <c r="E184" t="n">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="F184" t="n">
-        <v>1882</v>
+        <v>14601</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>9743.219999999999</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>20.72</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5616,22 +5616,22 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81- SP- Phrase</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>738.04</v>
+        <v>1027.44</v>
       </c>
       <c r="E186" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F186" t="n">
-        <v>5575</v>
+        <v>31210</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5644,28 +5644,1008 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>7198.37</v>
+      </c>
+      <c r="E187" t="n">
+        <v>883</v>
+      </c>
+      <c r="F187" t="n">
+        <v>219263</v>
+      </c>
+      <c r="G187" t="n">
+        <v>21345.74</v>
+      </c>
+      <c r="H187" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>2520.95</v>
+      </c>
+      <c r="E189" t="n">
+        <v>173</v>
+      </c>
+      <c r="F189" t="n">
+        <v>22232</v>
+      </c>
+      <c r="G189" t="n">
+        <v>5372.03</v>
+      </c>
+      <c r="H189" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(1)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>328.46</v>
+      </c>
+      <c r="E190" t="n">
+        <v>23</v>
+      </c>
+      <c r="F190" t="n">
+        <v>2438</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(2)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>763.2</v>
+      </c>
+      <c r="E191" t="n">
+        <v>52</v>
+      </c>
+      <c r="F191" t="n">
+        <v>3171</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>B0DCK4DR1B</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="E193" t="n">
+        <v>4</v>
+      </c>
+      <c r="F193" t="n">
+        <v>317</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1244.92</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>B0DFCG2VGS</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>3045.59</v>
+      </c>
+      <c r="E195" t="n">
+        <v>117</v>
+      </c>
+      <c r="F195" t="n">
+        <v>8793</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>4932.41</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1184</v>
+      </c>
+      <c r="F197" t="n">
+        <v>164290</v>
+      </c>
+      <c r="G197" t="n">
+        <v>7624.59</v>
+      </c>
+      <c r="H197" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1275.13</v>
+      </c>
+      <c r="E198" t="n">
+        <v>100</v>
+      </c>
+      <c r="F198" t="n">
+        <v>10290</v>
+      </c>
+      <c r="G198" t="n">
+        <v>5083.06</v>
+      </c>
+      <c r="H198" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>3516.2</v>
+      </c>
+      <c r="E201" t="n">
+        <v>216</v>
+      </c>
+      <c r="F201" t="n">
+        <v>63229</v>
+      </c>
+      <c r="G201" t="n">
+        <v>10334.75</v>
+      </c>
+      <c r="H201" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>B08L46ZKKZ</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>B0FNQS4RRD</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP-01</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>256.21</v>
+      </c>
+      <c r="E204" t="n">
+        <v>17</v>
+      </c>
+      <c r="F204" t="n">
+        <v>4427</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>5563.4</v>
+      </c>
+      <c r="E205" t="n">
+        <v>331</v>
+      </c>
+      <c r="F205" t="n">
+        <v>87474</v>
+      </c>
+      <c r="G205" t="n">
+        <v>40620.36</v>
+      </c>
+      <c r="H205" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>126.07</v>
+      </c>
+      <c r="E206" t="n">
+        <v>8</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1018</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>736.72</v>
+      </c>
+      <c r="E210" t="n">
+        <v>48</v>
+      </c>
+      <c r="F210" t="n">
+        <v>4135</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT01</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1996.17</v>
+      </c>
+      <c r="E211" t="n">
+        <v>128</v>
+      </c>
+      <c r="F211" t="n">
+        <v>18098</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>2338.3</v>
+      </c>
+      <c r="E213" t="n">
+        <v>90</v>
+      </c>
+      <c r="F213" t="n">
+        <v>7950</v>
+      </c>
+      <c r="G213" t="n">
+        <v>10167.8</v>
+      </c>
+      <c r="H213" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop-B0D2LJSQXZ-Phrase-SP</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>B0D2LJSQXZ</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>7</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>3514.41</v>
+      </c>
+      <c r="E217" t="n">
+        <v>257</v>
+      </c>
+      <c r="F217" t="n">
+        <v>111106</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1439.83</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="E218" t="n">
+        <v>58</v>
+      </c>
+      <c r="F218" t="n">
+        <v>9670</v>
+      </c>
+      <c r="G218" t="n">
+        <v>7140</v>
+      </c>
+      <c r="H218" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>384.42</v>
+      </c>
+      <c r="E219" t="n">
+        <v>16</v>
+      </c>
+      <c r="F219" t="n">
+        <v>3876</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-BM</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="E220" t="n">
+        <v>8</v>
+      </c>
+      <c r="F220" t="n">
+        <v>590</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1587.78</v>
+      </c>
+      <c r="E221" t="n">
+        <v>115</v>
+      </c>
+      <c r="F221" t="n">
+        <v>13695</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
           <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D187" t="n">
-        <v>354.05</v>
-      </c>
-      <c r="E187" t="n">
-        <v>18</v>
-      </c>
-      <c r="F187" t="n">
-        <v>1235</v>
-      </c>
-      <c r="G187" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" t="n">
-        <v>0</v>
+      <c r="D222" t="n">
+        <v>1315.44</v>
+      </c>
+      <c r="E222" t="n">
+        <v>62</v>
+      </c>
+      <c r="F222" t="n">
+        <v>5653</v>
+      </c>
+      <c r="G222" t="n">
+        <v>3219.49</v>
+      </c>
+      <c r="H222" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6885,13 +7865,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>207.59</v>
+        <v>668.9400000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F43" t="n">
-        <v>1467</v>
+        <v>5908</v>
       </c>
       <c r="G43" t="n">
         <v>5083.9</v>
@@ -7115,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>131</v>
+        <v>443</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -7171,7 +8151,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>63</v>
+        <v>335</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -7193,13 +8173,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>291</v>
+        <v>2374</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -7227,7 +8207,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -7247,7 +8227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7310,13 +8290,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1753</v>
+        <v>5594</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>319.21</v>
+        <v>986.36</v>
       </c>
       <c r="G2" t="n">
         <v>2541.53</v>
@@ -7343,13 +8323,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2396</v>
+        <v>4098</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>323.05</v>
+        <v>595.2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7376,13 +8356,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>18.91666666666667</v>
+        <v>106.3566666666667</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -7409,13 +8389,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>18.91666666666667</v>
+        <v>106.3566666666667</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7442,19 +8422,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4376</v>
+        <v>21462</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="F6" t="n">
-        <v>873.6366666666667</v>
+        <v>5051.986666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>2965.25</v>
+        <v>6184.75</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -7475,19 +8455,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10701</v>
+        <v>48542</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>268</v>
       </c>
       <c r="F7" t="n">
-        <v>1105.67</v>
+        <v>4600.58</v>
       </c>
       <c r="G7" t="n">
-        <v>2856.19</v>
+        <v>11424.76</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -7508,19 +8488,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3775</v>
+        <v>7642</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
-        <v>449.44</v>
+        <v>907.2095949367088</v>
       </c>
       <c r="G8" t="n">
-        <v>1046.67</v>
+        <v>3140</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7532,28 +8512,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1640</v>
+        <v>11584</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="F9" t="n">
-        <v>49.28333333333333</v>
+        <v>1375.260405063291</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4760</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7570,23 +8550,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1640</v>
+        <v>18464</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>49.28333333333333</v>
+        <v>748.37</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -7598,22 +8578,22 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1640</v>
+        <v>11578</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>193</v>
       </c>
       <c r="F11" t="n">
-        <v>49.28333333333333</v>
+        <v>2045.77</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -7631,7 +8611,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7640,19 +8620,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1695</v>
+        <v>10801</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="F12" t="n">
-        <v>254.88</v>
+        <v>1532.84</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>5057.64</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -7664,7 +8644,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7673,19 +8653,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3243</v>
+        <v>10409</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="F13" t="n">
-        <v>317.86</v>
+        <v>1419.49</v>
       </c>
       <c r="G13" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -7697,7 +8677,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7706,13 +8686,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2471</v>
+        <v>2339</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
-        <v>331.18</v>
+        <v>253.4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -7735,17 +8715,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>203</v>
+        <v>2339</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>50.48</v>
+        <v>253.4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -7768,17 +8748,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>203</v>
+        <v>2339</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
-        <v>50.48</v>
+        <v>253.4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -7796,28 +8776,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>203</v>
+        <v>3080</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>50.48</v>
+        <v>755</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>5083.06</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -7829,22 +8809,22 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>633</v>
+        <v>282</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>149.87</v>
+        <v>139.02</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -7867,17 +8847,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>282</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>29.14</v>
+        <v>139.02</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -7895,28 +8875,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>3086</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>29.14</v>
+        <v>422.94</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7928,7 +8908,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7937,13 +8917,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>297</v>
+        <v>16121</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="F21" t="n">
-        <v>96.67</v>
+        <v>1690.53</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -7961,28 +8941,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5276</v>
+        <v>3543</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="F22" t="n">
-        <v>515.29</v>
+        <v>1030.089752251336</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4066.940000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -7999,23 +8979,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709</v>
+        <v>2878</v>
       </c>
       <c r="E23" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
-        <v>405.86</v>
+        <v>836.9102477486643</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8036,16 +9016,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>114</v>
+        <v>452</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>21.75333333333333</v>
+        <v>114.4233333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -8069,16 +9049,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>114</v>
+        <v>452</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>21.75333333333333</v>
+        <v>114.4233333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -8102,16 +9082,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>114</v>
+        <v>452</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>21.75333333333333</v>
+        <v>114.4233333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -8135,13 +9115,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2584</v>
+        <v>16616</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="F27" t="n">
-        <v>319.11</v>
+        <v>2191.92</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -8164,23 +9144,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2582</v>
+        <v>20511</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>204</v>
       </c>
       <c r="F28" t="n">
-        <v>318.32</v>
+        <v>2252.16</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>10168.64</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -8192,7 +9172,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8201,13 +9181,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2018</v>
+        <v>133</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>234.69</v>
+        <v>12.69</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -8225,7 +9205,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8234,13 +9214,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2934</v>
+        <v>7543</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F30" t="n">
-        <v>144.29</v>
+        <v>913.79</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -8258,25 +9238,25 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1125</v>
+        <v>10604</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="F31" t="n">
-        <v>47.67333333333334</v>
+        <v>573.79</v>
       </c>
       <c r="G31" t="n">
-        <v>988.4166666666666</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -8300,19 +9280,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1125</v>
+        <v>16261</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="F32" t="n">
-        <v>47.67333333333334</v>
+        <v>740.99</v>
       </c>
       <c r="G32" t="n">
-        <v>988.4166666666666</v>
+        <v>9235.59</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -8324,28 +9304,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1125</v>
+        <v>4909</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F33" t="n">
-        <v>47.67333333333334</v>
+        <v>502.2889268752047</v>
       </c>
       <c r="G33" t="n">
-        <v>988.4166666666666</v>
+        <v>3219.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -8362,23 +9342,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3842</v>
+        <v>18925</v>
       </c>
       <c r="E34" t="n">
-        <v>35</v>
+        <v>237</v>
       </c>
       <c r="F34" t="n">
-        <v>296.2059727555682</v>
+        <v>1936.431073124795</v>
       </c>
       <c r="G34" t="n">
-        <v>3219.5</v>
+        <v>12411.86</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -8390,25 +9370,25 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3539</v>
+        <v>724</v>
       </c>
       <c r="E35" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F35" t="n">
-        <v>272.8140272444319</v>
+        <v>579.7454791149779</v>
       </c>
       <c r="G35" t="n">
-        <v>2965.25</v>
+        <v>3324.664340316445</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -8428,20 +9408,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4137</v>
+        <v>4348</v>
       </c>
       <c r="E36" t="n">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="F36" t="n">
-        <v>2922.42</v>
+        <v>3479.047708985496</v>
       </c>
       <c r="G36" t="n">
-        <v>17846.61</v>
+        <v>19951.28254209249</v>
       </c>
       <c r="H36" t="n">
         <v>6</v>
@@ -8456,28 +9436,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>10585</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>8470.568850044219</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>48576.14110407251</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -8489,28 +9469,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>410</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>328.437961855307</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1883.49201351856</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -8527,17 +9507,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>6.59</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -8555,22 +9535,22 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>14.81333333333333</v>
+        <v>6.59</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -8588,22 +9568,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>14.81333333333333</v>
+        <v>6.59</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -8626,25 +9606,190 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>311</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>43.68666666666667</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>311</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>43.68666666666667</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>B0DKJSCLBD</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>58</v>
-      </c>
-      <c r="E42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" t="n">
-        <v>14.81333333333333</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="D44" t="n">
+        <v>311</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>43.68666666666667</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>16041</v>
+      </c>
+      <c r="E45" t="n">
+        <v>78</v>
+      </c>
+      <c r="F45" t="n">
+        <v>896.78</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>8476</v>
+      </c>
+      <c r="E46" t="n">
+        <v>49</v>
+      </c>
+      <c r="F46" t="n">
+        <v>572.61</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>125</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77.61</v>
+        <v>102.49</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>716</v>
+        <v>857</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2284.47</v>
+        <v>2894.3</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>14131</v>
+        <v>18468</v>
       </c>
       <c r="G6" t="n">
         <v>10168.64</v>
@@ -703,7 +703,7 @@
         <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>4440</v>
+        <v>4439</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>663.16</v>
+        <v>874.92</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>9398</v>
+        <v>12226</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>490.32</v>
+        <v>844.17</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>7026</v>
+        <v>9967</v>
       </c>
       <c r="G13" t="n">
-        <v>1244.92</v>
+        <v>2489.84</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2467.99</v>
+        <v>3383.76</v>
       </c>
       <c r="E16" t="n">
-        <v>354</v>
+        <v>466</v>
       </c>
       <c r="F16" t="n">
-        <v>30260</v>
+        <v>39606</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -912,63 +912,63 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev - B0DNJP9T35 - Spin Scrubber- SP - PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6865.62</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>119888</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>12709.33</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3032.48</v>
+        <v>9681.969999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>195</v>
+        <v>512</v>
       </c>
       <c r="F19" t="n">
-        <v>43729</v>
+        <v>165035</v>
       </c>
       <c r="G19" t="n">
-        <v>5168.64</v>
+        <v>12709.33</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4447.2</v>
+        <v>5342.8</v>
       </c>
       <c r="E20" t="n">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="F20" t="n">
-        <v>23077</v>
+        <v>72126</v>
       </c>
       <c r="G20" t="n">
-        <v>20335.6</v>
+        <v>20420.34</v>
       </c>
       <c r="H20" t="n">
         <v>4</v>
@@ -996,7 +996,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT - SP</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1005,26 +1005,26 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2415.76</v>
+        <v>6546.849999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>125</v>
+        <v>430</v>
       </c>
       <c r="F21" t="n">
-        <v>11707</v>
+        <v>30642</v>
       </c>
       <c r="G21" t="n">
-        <v>15251.7</v>
+        <v>20335.6</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT -SP</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT - SP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1033,82 +1033,82 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>510.2</v>
+        <v>3413.72</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="F22" t="n">
-        <v>3762</v>
+        <v>16025</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>15251.7</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT -SP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>873.23</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>5495</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4171.96</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>105090</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>12622.05</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1117,26 +1117,26 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3234.86</v>
+        <v>6152.82</v>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>418</v>
       </c>
       <c r="F25" t="n">
-        <v>45586</v>
+        <v>155438</v>
       </c>
       <c r="G25" t="n">
-        <v>10589</v>
+        <v>14739.85</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(1)</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1145,26 +1145,26 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>822.59</v>
+        <v>4189.53</v>
       </c>
       <c r="E26" t="n">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="F26" t="n">
-        <v>17688</v>
+        <v>56003</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>10589</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(2)</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(1)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>370.16</v>
+        <v>1006.25</v>
       </c>
       <c r="E27" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>6747</v>
+        <v>21842</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,22 +1192,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - AT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(2)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1045.3</v>
+        <v>606.05</v>
       </c>
       <c r="E28" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="F28" t="n">
-        <v>1944</v>
+        <v>11624</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - PT</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - AT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>360.29</v>
+        <v>1625.2</v>
       </c>
       <c r="E29" t="n">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="F29" t="n">
-        <v>7581</v>
+        <v>3485</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - PT(1)</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - PT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>185.43</v>
+        <v>580.2</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F30" t="n">
-        <v>2643</v>
+        <v>11983</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - Phrase</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - PT(1)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>359.86</v>
+        <v>286.17</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F31" t="n">
-        <v>6794</v>
+        <v>3954</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1304,22 +1304,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - AT</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1153.72</v>
+        <v>437.49</v>
       </c>
       <c r="E32" t="n">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="F32" t="n">
-        <v>31660</v>
+        <v>8495</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - PT</t>
+          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - AT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1341,54 +1341,54 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>179.22</v>
+        <v>1369.81</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="F33" t="n">
-        <v>4361</v>
+        <v>34056</v>
       </c>
       <c r="G33" t="n">
-        <v>11863.56</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - PT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>355.02</v>
+        <v>293.62</v>
       </c>
       <c r="E34" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>12762</v>
+        <v>6252</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>11863.56</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier- PT</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.9</v>
+        <v>562.52</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F35" t="n">
-        <v>673</v>
+        <v>16792</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,22 +1416,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier- PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>100.27</v>
+        <v>49.27</v>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>1228</v>
+        <v>1070</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,22 +1444,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>100.27</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1601</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,12 +1472,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-CT</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1500,7 +1500,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>211.33</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1537,125 +1537,125 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1773.53</v>
+        <v>316.01</v>
       </c>
       <c r="E40" t="n">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>3687</v>
+        <v>333</v>
       </c>
       <c r="G40" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8613.4</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>10393</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>20335.6</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2088.89</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>5567</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>5083.06</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>12440.78</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>14611</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>30503.4</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>572.4</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>4612</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,50 +1668,50 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - AT</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2400.78</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>41622</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>6184.75</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - CT</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1483.81</v>
+        <v>572.4</v>
       </c>
       <c r="E46" t="n">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="F46" t="n">
-        <v>9811</v>
+        <v>4611</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - AT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1733,41 +1733,41 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>876.84</v>
+        <v>3170.42</v>
       </c>
       <c r="E47" t="n">
-        <v>47</v>
+        <v>542</v>
       </c>
       <c r="F47" t="n">
-        <v>5658</v>
+        <v>54664</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>6184.75</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - CT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>23.6</v>
+        <v>2106.05</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="F48" t="n">
-        <v>1609</v>
+        <v>16247</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,40 +1780,40 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - PT</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>61.11</v>
+        <v>995.13</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F49" t="n">
-        <v>131</v>
+        <v>6193</v>
       </c>
       <c r="G49" t="n">
-        <v>5253.39</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1836,22 +1836,22 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>225.65</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1225.65</v>
+        <v>45.31</v>
       </c>
       <c r="E52" t="n">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>12848</v>
+        <v>1888</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1892,78 +1892,78 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>61.11</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>5253.39</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT</t>
+          <t>Nexlev- B0DJFH6RTL-Portable Tyre Inflator-SP-PT-exact</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3417.66</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>12024</v>
+        <v>15</v>
       </c>
       <c r="G54" t="n">
-        <v>2880.51</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT-Refine</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2322.44</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>7432</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1976,35 +1976,35 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-PT</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3781.32</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>9184</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>7963.570000000001</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2013,69 +2013,69 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>162.04</v>
+        <v>1340.84</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="F57" t="n">
-        <v>780</v>
+        <v>14564</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16189.88</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>418</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>146034</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>18811.02</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa  Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>206.05</v>
+        <v>272.21</v>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F59" t="n">
-        <v>949</v>
+        <v>489</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,50 +2088,50 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>755.5599999999999</v>
+        <v>3593.21</v>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>269</v>
       </c>
       <c r="F60" t="n">
-        <v>12378</v>
+        <v>13231</v>
       </c>
       <c r="G60" t="n">
-        <v>2093.33</v>
+        <v>2880.51</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT-Refine</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9.870000000000001</v>
+        <v>2796.87</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>221</v>
       </c>
       <c r="F61" t="n">
-        <v>94</v>
+        <v>8436</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2144,50 +2144,50 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1222.32</v>
+        <v>5575.21</v>
       </c>
       <c r="E62" t="n">
-        <v>52</v>
+        <v>423</v>
       </c>
       <c r="F62" t="n">
-        <v>24883</v>
+        <v>13934</v>
       </c>
       <c r="G62" t="n">
-        <v>4319.51</v>
+        <v>12789.86</v>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>802.79</v>
+        <v>162.04</v>
       </c>
       <c r="E63" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
-        <v>7291</v>
+        <v>780</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,50 +2200,50 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>16189.88</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>145893</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>18811.02</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6.14</v>
+        <v>472.84</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>26</v>
+        <v>1567</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2256,22 +2256,22 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
+          <t>Nexlev-B0D672NXC8-Steam cleaner-KT-BM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>619.1700000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>3471</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2284,22 +2284,22 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Sofa Cleaning Machine-SP-PT</t>
+          <t>Nexlev-B0D672NXC8-Steam cleaner-KT-Phrase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>482.84</v>
+        <v>151.45</v>
       </c>
       <c r="E67" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F67" t="n">
-        <v>2293</v>
+        <v>4546</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,22 +2312,22 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-B0D672NXC8-Steam cleaner-SP-PT-exact</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1758.59</v>
+        <v>552.09</v>
       </c>
       <c r="E68" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F68" t="n">
-        <v>13066</v>
+        <v>770</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2340,50 +2340,50 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>888.16</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>15195</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2093.33</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>25.01</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2396,162 +2396,162 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D845B2DG-Lint Remover-SP-CT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1437.63</v>
+        <v>31.34</v>
       </c>
       <c r="E71" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>21525</v>
+        <v>96</v>
       </c>
       <c r="G71" t="n">
-        <v>6853.34</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-AT</t>
+          <t>Nexlev-B0D9KFP4MG-Sraightener Brush-KT-Phrase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1488.12</v>
+        <v>200.12</v>
       </c>
       <c r="E72" t="n">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>31182</v>
+        <v>9465</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1651.69</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
+          <t>Nexlev-B0D9KFP4MG-Straightener Brush-SP-PT-exact</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7456.45</v>
+        <v>13.03</v>
       </c>
       <c r="E73" t="n">
-        <v>341</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>77859</v>
+        <v>312</v>
       </c>
       <c r="G73" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>9073.959999999999</v>
+        <v>1222.32</v>
       </c>
       <c r="E74" t="n">
-        <v>399</v>
+        <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>32827</v>
+        <v>24883</v>
       </c>
       <c r="G74" t="n">
-        <v>20335.6</v>
+        <v>4319.51</v>
       </c>
       <c r="H74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4790.49</v>
+        <v>836.67</v>
       </c>
       <c r="E75" t="n">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="F75" t="n">
-        <v>13102</v>
+        <v>7621</v>
       </c>
       <c r="G75" t="n">
-        <v>16691.53</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop cleaner-SP-PT</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>719.1800000000001</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>5406</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,134 +2564,134 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1255.86</v>
+        <v>39.96</v>
       </c>
       <c r="E77" t="n">
-        <v>142</v>
+        <v>3</v>
       </c>
       <c r="F77" t="n">
-        <v>17502</v>
+        <v>409</v>
       </c>
       <c r="G77" t="n">
-        <v>5209.32</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3528.79</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>71501</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>12155.08</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev-B0DCK3N2JJ-Straightener Brush-KT-BM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10727.98</v>
+        <v>193.09</v>
       </c>
       <c r="E79" t="n">
-        <v>870</v>
+        <v>20</v>
       </c>
       <c r="F79" t="n">
-        <v>460217</v>
+        <v>1426</v>
       </c>
       <c r="G79" t="n">
-        <v>30503.4</v>
+        <v>2287.29</v>
       </c>
       <c r="H79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DCK3N2JJ-Straightener Brush-SP-PT-exact</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4140.73</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>54179</v>
+        <v>185</v>
       </c>
       <c r="G80" t="n">
-        <v>15251.7</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev-B0DCK7ZH5P-Sofa Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>838.13</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>3415</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2704,22 +2704,22 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1758.59</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>13066</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2732,78 +2732,78 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4201.41</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>240634</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>6268.650000000001</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-B0DFCDZWND-Heating Pad-KT-Phrase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2929.5</v>
+        <v>11.05</v>
       </c>
       <c r="E84" t="n">
-        <v>271</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>91072</v>
+        <v>28</v>
       </c>
       <c r="G84" t="n">
-        <v>10250</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-BM</t>
+          <t>Nexlev-B0DFCDZWND-Heating Pad-SP-PT-exact</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1101.18</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>4361</v>
+        <v>7</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2816,22 +2816,22 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-PT</t>
+          <t>Nexlev-B0DJFH6RTL-Portable Tyre Inflator-SP-AT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1313.94</v>
+        <v>497.75</v>
       </c>
       <c r="E86" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>3123</v>
+        <v>13798</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2844,22 +2844,22 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>626.14</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>2662</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,81 +2872,81 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>527.3399999999999</v>
+        <v>2008.69</v>
       </c>
       <c r="E88" t="n">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="F88" t="n">
-        <v>9161</v>
+        <v>28686</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>6853.34</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-AT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2221.04</v>
+        <v>1713.9</v>
       </c>
       <c r="E89" t="n">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="F89" t="n">
-        <v>14562</v>
+        <v>35900</v>
       </c>
       <c r="G89" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2267.86</v>
+        <v>9919.889999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>165</v>
+        <v>447</v>
       </c>
       <c r="F90" t="n">
-        <v>28083</v>
+        <v>104079</v>
       </c>
       <c r="G90" t="n">
-        <v>6608.48</v>
+        <v>11692.38</v>
       </c>
       <c r="H90" t="n">
         <v>3</v>
@@ -2956,78 +2956,78 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>11000.56</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>38733</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>35587.3</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>30.8</v>
+        <v>6933.12</v>
       </c>
       <c r="E92" t="n">
+        <v>219</v>
+      </c>
+      <c r="F92" t="n">
+        <v>16569</v>
+      </c>
+      <c r="G92" t="n">
+        <v>16691.53</v>
+      </c>
+      <c r="H92" t="n">
         <v>4</v>
-      </c>
-      <c r="F92" t="n">
-        <v>553</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1464.12</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F93" t="n">
-        <v>197</v>
+        <v>11251</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,78 +3040,78 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>19.76</v>
+        <v>1585.26</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>177</v>
       </c>
       <c r="F94" t="n">
-        <v>26</v>
+        <v>22293</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>6945.76</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6.67</v>
+        <v>4829.33</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>452</v>
       </c>
       <c r="F95" t="n">
-        <v>102</v>
+        <v>96181</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>12155.08</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush-PT-exact</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>52.51</v>
+        <v>53.47</v>
       </c>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F96" t="n">
-        <v>319</v>
+        <v>1545</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,22 +3124,22 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush-PT-exact(2)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>7.95</v>
+        <v>22.18</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F97" t="n">
-        <v>179</v>
+        <v>344</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3152,68 +3152,68 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>29.5</v>
+        <v>15379.92</v>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>1265</v>
       </c>
       <c r="F98" t="n">
-        <v>120</v>
+        <v>678723</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>30503.4</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>67.55</v>
+        <v>6049.780000000001</v>
       </c>
       <c r="E99" t="n">
-        <v>11</v>
+        <v>332</v>
       </c>
       <c r="F99" t="n">
-        <v>728</v>
+        <v>77544</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>15251.7</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3236,12 +3236,12 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3264,50 +3264,50 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FPGDVVCX-Calf Massager-SP-At</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>53.36</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>112</v>
+        <v>765</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>5712.38</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FPGDVVCX-Calf Massager-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>17.77</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3320,78 +3320,78 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>8.17</v>
+        <v>4548.4</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>409</v>
       </c>
       <c r="F104" t="n">
-        <v>68</v>
+        <v>262398</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>6268.650000000001</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>75.28</v>
+        <v>4566.14</v>
       </c>
       <c r="E105" t="n">
-        <v>9</v>
+        <v>425</v>
       </c>
       <c r="F105" t="n">
-        <v>390</v>
+        <v>138933</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>16603.4</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-BM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1697.49</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>6586</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3404,22 +3404,22 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>22.12</v>
+        <v>2293.36</v>
       </c>
       <c r="E107" t="n">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="F107" t="n">
-        <v>558</v>
+        <v>5481</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3432,50 +3432,50 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1276.08</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F108" t="n">
-        <v>63</v>
+        <v>5881</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>956.1799999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F109" t="n">
-        <v>136</v>
+        <v>13584</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3488,56 +3488,56 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>2255.35</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="F110" t="n">
-        <v>107</v>
+        <v>14886</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7.77</v>
+        <v>3536.25</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="F111" t="n">
-        <v>133</v>
+        <v>34099</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>6608.48</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.21</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>1314</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3577,23 +3577,23 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5.43</v>
+        <v>30.8</v>
       </c>
       <c r="E113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F113" t="n">
-        <v>40</v>
+        <v>553</v>
       </c>
       <c r="G113" t="n">
-        <v>931.36</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0F74DJYG6</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3633,17 +3633,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>26.21</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F115" t="n">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3661,17 +3661,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>14.62</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F116" t="n">
-        <v>274</v>
+        <v>205</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3689,17 +3689,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>44.13</v>
+        <v>60.62</v>
       </c>
       <c r="E117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F117" t="n">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3717,17 +3717,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>32.2</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F118" t="n">
-        <v>102</v>
+        <v>280</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3745,45 +3745,45 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>138.84</v>
+        <v>29.5</v>
       </c>
       <c r="E119" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>3927</v>
+        <v>165</v>
       </c>
       <c r="G119" t="n">
-        <v>8466.1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>39.82</v>
+        <v>125.15</v>
       </c>
       <c r="E120" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F120" t="n">
-        <v>3270</v>
+        <v>1496</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3796,22 +3796,22 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4.91</v>
+        <v>16.73</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>344</v>
+        <v>93</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3824,12 +3824,12 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3852,22 +3852,22 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>12</v>
+        <v>212</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3880,12 +3880,12 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>303</v>
+        <v>14</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3908,22 +3908,22 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>34.7</v>
+        <v>8.17</v>
       </c>
       <c r="E125" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>1088</v>
+        <v>156</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3936,22 +3936,22 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>32.42</v>
+        <v>109.14</v>
       </c>
       <c r="E126" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F126" t="n">
-        <v>1613</v>
+        <v>678</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3964,50 +3964,50 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>27.11</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>4746</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>761.86</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4.8</v>
+        <v>22.12</v>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" t="n">
-        <v>592</v>
+        <v>891</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -4020,12 +4020,12 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4048,50 +4048,50 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>198.83</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>14496</v>
+        <v>273</v>
       </c>
       <c r="G130" t="n">
-        <v>4955.09</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>14.13</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>370</v>
+        <v>205</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4104,22 +4104,22 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>36.21</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="E132" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>1291</v>
+        <v>316</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -4132,22 +4132,22 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>11.21</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -4160,50 +4160,50 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>931.36</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0F74DJYG6</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>67</v>
+        <v>7.07</v>
       </c>
       <c r="E135" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>5149</v>
+        <v>2396</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4216,22 +4216,22 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>185.02</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>5503</v>
+        <v>332</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -4244,22 +4244,22 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4272,22 +4272,22 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.37</v>
+        <v>69.09</v>
       </c>
       <c r="E138" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F138" t="n">
-        <v>192</v>
+        <v>2403</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4300,22 +4300,22 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>24.78</v>
+        <v>4.81</v>
       </c>
       <c r="E139" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>894</v>
+        <v>735</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4328,50 +4328,50 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>298.62</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>8679</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>75.38999999999999</v>
+        <v>154</v>
       </c>
       <c r="E141" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F141" t="n">
-        <v>12455</v>
+        <v>9746</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4384,22 +4384,22 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>23.22</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4412,12 +4412,12 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4440,22 +4440,22 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>220</v>
+        <v>43</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4501,17 +4501,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>5.07</v>
+        <v>56.5</v>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F146" t="n">
-        <v>295</v>
+        <v>1578</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>32.42</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F147" t="n">
-        <v>12</v>
+        <v>2059</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4557,23 +4557,23 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>7.02</v>
+        <v>35.87</v>
       </c>
       <c r="E148" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F148" t="n">
-        <v>399</v>
+        <v>6441</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>761.86</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4585,17 +4585,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>7.54</v>
+        <v>15.67</v>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F149" t="n">
-        <v>129</v>
+        <v>770</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4613,23 +4613,23 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>14.45</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>12540.68</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -4641,23 +4641,23 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>29.8</v>
+        <v>270.58</v>
       </c>
       <c r="E151" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="F151" t="n">
-        <v>1117</v>
+        <v>20415</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>6606.78</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -4697,17 +4697,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>14.13</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F153" t="n">
-        <v>578</v>
+        <v>489</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4725,17 +4725,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0F74DJYG6</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>14.83</v>
+        <v>46.99</v>
       </c>
       <c r="E154" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F154" t="n">
-        <v>372</v>
+        <v>1475</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4781,23 +4781,23 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>44.36</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>3623</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>677.12</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -4809,17 +4809,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>8.029999999999999</v>
+        <v>78.71000000000001</v>
       </c>
       <c r="E157" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F157" t="n">
-        <v>524</v>
+        <v>7014</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4837,23 +4837,23 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>244.2</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F158" t="n">
-        <v>111</v>
+        <v>8401</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1016.1</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -4865,45 +4865,45 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>227.77</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>9063</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>8466.1</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>11.37</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4916,12 +4916,12 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4944,40 +4944,40 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>31.48</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F162" t="n">
-        <v>28</v>
+        <v>1225</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1185.59</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -4987,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5000,22 +5000,22 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>156.64</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F164" t="n">
-        <v>386</v>
+        <v>23129</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5028,22 +5028,22 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5056,22 +5056,22 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5084,22 +5084,22 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5.28</v>
+        <v>7.899999999999999</v>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" t="n">
-        <v>127</v>
+        <v>350</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -5112,12 +5112,12 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -5140,22 +5140,22 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>9.17</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F169" t="n">
-        <v>23</v>
+        <v>413</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -5168,12 +5168,12 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -5183,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3.62</v>
+        <v>11.02</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F171" t="n">
-        <v>5</v>
+        <v>637</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>7.54</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F172" t="n">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5261,41 +5261,41 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F173" t="n">
-        <v>5</v>
+        <v>562</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>12540.68</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>29.8</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F174" t="n">
-        <v>10</v>
+        <v>1198</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -5308,12 +5308,12 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -5323,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -5336,50 +5336,50 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>40</v>
+        <v>722</v>
       </c>
       <c r="G176" t="n">
-        <v>233.05</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0F74DJYG6</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>23.62</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5392,22 +5392,22 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>17.1</v>
+        <v>4.04</v>
       </c>
       <c r="E178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F178" t="n">
-        <v>212</v>
+        <v>1388</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5420,50 +5420,50 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>48.37</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>5114</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>677.12</v>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>94.59</v>
+        <v>11.24</v>
       </c>
       <c r="E180" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F180" t="n">
-        <v>702</v>
+        <v>934</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5476,12 +5476,12 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -5491,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5504,50 +5504,50 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>343.89</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>12280</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>747.55</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>6629</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5560,40 +5560,40 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1290.98</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>14601</v>
+        <v>25</v>
       </c>
       <c r="G184" t="n">
-        <v>9743.219999999999</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5616,22 +5616,22 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81- SP- Phrase</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1027.44</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>31210</v>
+        <v>64</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5644,50 +5644,50 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>7198.37</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>219263</v>
+        <v>564</v>
       </c>
       <c r="G187" t="n">
-        <v>21345.74</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5700,50 +5700,50 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2520.95</v>
+        <v>4.27</v>
       </c>
       <c r="E189" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>22232</v>
+        <v>12</v>
       </c>
       <c r="G189" t="n">
-        <v>5372.03</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(1)</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>328.46</v>
+        <v>11.23</v>
       </c>
       <c r="E190" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F190" t="n">
-        <v>2438</v>
+        <v>201</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5756,22 +5756,22 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(2)</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>763.2</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>3171</v>
+        <v>22</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5784,12 +5784,12 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -5799,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5812,50 +5812,50 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>56.58</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>317</v>
+        <v>24</v>
       </c>
       <c r="G193" t="n">
-        <v>1244.92</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5868,22 +5868,22 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3045.59</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>8793</v>
+        <v>161</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5896,12 +5896,12 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5924,78 +5924,78 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>4932.41</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>164290</v>
+        <v>2</v>
       </c>
       <c r="G197" t="n">
-        <v>7624.59</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1275.13</v>
+        <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>10290</v>
+        <v>19</v>
       </c>
       <c r="G198" t="n">
-        <v>5083.06</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -6008,78 +6008,78 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="G200" t="n">
-        <v>0</v>
+        <v>233.05</v>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>3516.2</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>63229</v>
+        <v>9</v>
       </c>
       <c r="G201" t="n">
-        <v>10334.75</v>
+        <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>B08L46ZKKZ</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>83.14</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -6092,12 +6092,12 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>B0FNQS4RRD</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -6120,22 +6120,22 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP-01</t>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>256.21</v>
+        <v>142.73</v>
       </c>
       <c r="E204" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F204" t="n">
-        <v>4427</v>
+        <v>1049</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6148,50 +6148,50 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>5563.4</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>87474</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>40620.36</v>
+        <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>126.07</v>
+        <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>1018</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -6204,22 +6204,22 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>1343.61</v>
       </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>13965</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -6232,35 +6232,35 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-PT-SP</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>1915.63</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>20348</v>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>12962.71</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6288,22 +6288,22 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81- SP- Phrase</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>736.72</v>
+        <v>1623.1</v>
       </c>
       <c r="E210" t="n">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="F210" t="n">
-        <v>4135</v>
+        <v>45811</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -6316,40 +6316,40 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT01</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1996.17</v>
+        <v>9479.59</v>
       </c>
       <c r="E211" t="n">
-        <v>128</v>
+        <v>1163</v>
       </c>
       <c r="F211" t="n">
-        <v>18098</v>
+        <v>295820</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>21345.74</v>
       </c>
       <c r="H211" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -6372,50 +6372,50 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2338.3</v>
+        <v>3735.49</v>
       </c>
       <c r="E213" t="n">
-        <v>90</v>
+        <v>257</v>
       </c>
       <c r="F213" t="n">
-        <v>7950</v>
+        <v>34721</v>
       </c>
       <c r="G213" t="n">
-        <v>10167.8</v>
+        <v>7150.849999999999</v>
       </c>
       <c r="H213" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(1)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>615.14</v>
       </c>
       <c r="E214" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F214" t="n">
-        <v>0</v>
+        <v>3523</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6428,40 +6428,40 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop-B0D2LJSQXZ-Phrase-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(2)</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0</v>
+        <v>1178.12</v>
       </c>
       <c r="E215" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F215" t="n">
-        <v>7</v>
+        <v>5126</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>4066.94</v>
       </c>
       <c r="H215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -6484,25 +6484,25 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>3514.41</v>
+        <v>56.58</v>
       </c>
       <c r="E217" t="n">
-        <v>257</v>
+        <v>4</v>
       </c>
       <c r="F217" t="n">
-        <v>111106</v>
+        <v>645</v>
       </c>
       <c r="G217" t="n">
-        <v>1439.83</v>
+        <v>1244.92</v>
       </c>
       <c r="H217" t="n">
         <v>1</v>
@@ -6512,78 +6512,78 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>659.22</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>9670</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>7140</v>
+        <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>384.42</v>
+        <v>3633.4</v>
       </c>
       <c r="E219" t="n">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="F219" t="n">
-        <v>3876</v>
+        <v>10893</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>1694.06</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-BM</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>50.45</v>
+        <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6596,55 +6596,727 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1587.78</v>
+        <v>6958.31</v>
       </c>
       <c r="E221" t="n">
-        <v>115</v>
+        <v>1649</v>
       </c>
       <c r="F221" t="n">
-        <v>13695</v>
+        <v>238786</v>
       </c>
       <c r="G221" t="n">
-        <v>0</v>
+        <v>10166.12</v>
       </c>
       <c r="H221" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>2076.13</v>
+      </c>
+      <c r="E222" t="n">
+        <v>161</v>
+      </c>
+      <c r="F222" t="n">
+        <v>17160</v>
+      </c>
+      <c r="G222" t="n">
+        <v>5083.06</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>4416.87</v>
+      </c>
+      <c r="E225" t="n">
+        <v>274</v>
+      </c>
+      <c r="F225" t="n">
+        <v>74282</v>
+      </c>
+      <c r="G225" t="n">
+        <v>12452.55</v>
+      </c>
+      <c r="H225" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>B08L46ZKKZ</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>B0FNQS4RRD</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP-01</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>564.84</v>
+      </c>
+      <c r="E228" t="n">
+        <v>37</v>
+      </c>
+      <c r="F228" t="n">
+        <v>10209</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>8346.119999999999</v>
+      </c>
+      <c r="E229" t="n">
+        <v>477</v>
+      </c>
+      <c r="F229" t="n">
+        <v>114212</v>
+      </c>
+      <c r="G229" t="n">
+        <v>66039.86</v>
+      </c>
+      <c r="H229" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>126.07</v>
+      </c>
+      <c r="E230" t="n">
+        <v>8</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1190</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1360.71</v>
+      </c>
+      <c r="E234" t="n">
+        <v>89</v>
+      </c>
+      <c r="F234" t="n">
+        <v>8424</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT01</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>3014.26</v>
+      </c>
+      <c r="E235" t="n">
+        <v>190</v>
+      </c>
+      <c r="F235" t="n">
+        <v>24614</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>3059.18</v>
+      </c>
+      <c r="E237" t="n">
+        <v>117</v>
+      </c>
+      <c r="F237" t="n">
+        <v>10243</v>
+      </c>
+      <c r="G237" t="n">
+        <v>10167.8</v>
+      </c>
+      <c r="H237" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop-B0D2LJSQXZ-Phrase-SP</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>B0D2LJSQXZ</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="n">
+        <v>23</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>4747.2</v>
+      </c>
+      <c r="E241" t="n">
+        <v>342</v>
+      </c>
+      <c r="F241" t="n">
+        <v>140768</v>
+      </c>
+      <c r="G241" t="n">
+        <v>8015.26</v>
+      </c>
+      <c r="H241" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1027.24</v>
+      </c>
+      <c r="E242" t="n">
+        <v>90</v>
+      </c>
+      <c r="F242" t="n">
+        <v>13872</v>
+      </c>
+      <c r="G242" t="n">
+        <v>11900</v>
+      </c>
+      <c r="H242" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>680.6</v>
+      </c>
+      <c r="E243" t="n">
+        <v>27</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6738</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-BM</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>251.75</v>
+      </c>
+      <c r="E244" t="n">
+        <v>36</v>
+      </c>
+      <c r="F244" t="n">
+        <v>2091</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1587.78</v>
+      </c>
+      <c r="E245" t="n">
+        <v>115</v>
+      </c>
+      <c r="F245" t="n">
+        <v>13694</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
           <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D222" t="n">
-        <v>1315.44</v>
-      </c>
-      <c r="E222" t="n">
-        <v>62</v>
-      </c>
-      <c r="F222" t="n">
-        <v>5653</v>
-      </c>
-      <c r="G222" t="n">
+      <c r="D246" t="n">
+        <v>1777.23</v>
+      </c>
+      <c r="E246" t="n">
+        <v>83</v>
+      </c>
+      <c r="F246" t="n">
+        <v>6882</v>
+      </c>
+      <c r="G246" t="n">
         <v>3219.49</v>
       </c>
-      <c r="H222" t="n">
+      <c r="H246" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7865,13 +8537,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>668.9400000000001</v>
+        <v>1017.85</v>
       </c>
       <c r="E43" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F43" t="n">
-        <v>5908</v>
+        <v>8959</v>
       </c>
       <c r="G43" t="n">
         <v>5083.9</v>
@@ -8095,7 +8767,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -8151,7 +8823,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>335</v>
+        <v>571</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -8179,7 +8851,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>2374</v>
+        <v>3078</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -8207,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -8227,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8290,13 +8962,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5594</v>
+        <v>7805</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="F2" t="n">
-        <v>986.36</v>
+        <v>1465.12</v>
       </c>
       <c r="G2" t="n">
         <v>2541.53</v>
@@ -8347,22 +9019,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>106.3566666666667</v>
+        <v>30.30333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -8380,22 +9052,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>106.3566666666667</v>
+        <v>30.30333333333333</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8413,28 +9085,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21462</v>
+        <v>131</v>
       </c>
       <c r="E6" t="n">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>5051.986666666667</v>
+        <v>30.30333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>6184.75</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8446,28 +9118,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48542</v>
+        <v>1569</v>
       </c>
       <c r="E7" t="n">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>4600.58</v>
+        <v>248.0633333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>11424.76</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8479,28 +9151,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7642</v>
+        <v>1569</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>907.2095949367088</v>
+        <v>248.0633333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>3140</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8512,28 +9184,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11584</v>
+        <v>1569</v>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>1375.260405063291</v>
+        <v>248.0633333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>4760</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8545,28 +9217,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18464</v>
+        <v>98</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>748.37</v>
+        <v>127.61</v>
       </c>
       <c r="G10" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8578,22 +9250,22 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11578</v>
+        <v>98</v>
       </c>
       <c r="E11" t="n">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>2045.77</v>
+        <v>127.61</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8611,25 +9283,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10801</v>
+        <v>24159</v>
       </c>
       <c r="E12" t="n">
-        <v>146</v>
+        <v>191</v>
       </c>
       <c r="F12" t="n">
-        <v>1532.84</v>
+        <v>6082.87</v>
       </c>
       <c r="G12" t="n">
-        <v>5057.64</v>
+        <v>6184.75</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
@@ -8644,28 +9316,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10409</v>
+        <v>63829</v>
       </c>
       <c r="E13" t="n">
-        <v>125</v>
+        <v>373</v>
       </c>
       <c r="F13" t="n">
-        <v>1419.49</v>
+        <v>6352.87</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>17108.59</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8677,28 +9349,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2339</v>
+        <v>9090</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="F14" t="n">
-        <v>253.4</v>
+        <v>1110.916101265823</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4804.060886075949</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8710,28 +9382,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2339</v>
+        <v>13779</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="F15" t="n">
-        <v>253.4</v>
+        <v>1684.063898734177</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>7282.58911392405</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8743,28 +9415,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2339</v>
+        <v>14408</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>253.4</v>
+        <v>625.7253013104111</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8808.975608171429</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8776,28 +9448,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3080</v>
+        <v>9844</v>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F17" t="n">
-        <v>755</v>
+        <v>427.5446986895889</v>
       </c>
       <c r="G17" t="n">
-        <v>5083.06</v>
+        <v>6018.984391828569</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8809,22 +9481,22 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>282</v>
+        <v>14042</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>247</v>
       </c>
       <c r="F18" t="n">
-        <v>139.02</v>
+        <v>2635.45</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8842,28 +9514,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>282</v>
+        <v>9645</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>139.02</v>
+        <v>1598.452309254072</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5057.64</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8875,25 +9547,25 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3086</v>
+        <v>3392</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F20" t="n">
-        <v>422.94</v>
+        <v>562.187690745928</v>
       </c>
       <c r="G20" t="n">
-        <v>5083.9</v>
+        <v>1778.81</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -8908,28 +9580,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16121</v>
+        <v>12966</v>
       </c>
       <c r="E21" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="F21" t="n">
-        <v>1690.53</v>
+        <v>1920.04</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2880.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -8941,28 +9613,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3543</v>
+        <v>2866</v>
       </c>
       <c r="E22" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
-        <v>1030.089752251336</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>4066.940000000001</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8974,28 +9646,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2878</v>
+        <v>2866</v>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>836.9102477486643</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9007,25 +9679,25 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>452</v>
+        <v>2866</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>114.4233333333333</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>777.6833333333334</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -9040,28 +9712,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>452</v>
+        <v>4348</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>114.4233333333333</v>
+        <v>1038.49</v>
       </c>
       <c r="G25" t="n">
-        <v>777.6833333333334</v>
+        <v>5083.06</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9073,25 +9745,25 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26" t="n">
-        <v>114.4233333333333</v>
+        <v>185.36</v>
       </c>
       <c r="G26" t="n">
-        <v>777.6833333333334</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -9106,22 +9778,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16616</v>
+        <v>418</v>
       </c>
       <c r="E27" t="n">
-        <v>204</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>2191.92</v>
+        <v>185.36</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -9139,25 +9811,25 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20511</v>
+        <v>4437</v>
       </c>
       <c r="E28" t="n">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>2252.16</v>
+        <v>589.86</v>
       </c>
       <c r="G28" t="n">
-        <v>10168.64</v>
+        <v>5083.9</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -9172,22 +9844,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>133</v>
+        <v>25212</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F29" t="n">
-        <v>12.69</v>
+        <v>2621.57</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -9205,28 +9877,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7543</v>
+        <v>4645</v>
       </c>
       <c r="E30" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="F30" t="n">
-        <v>913.79</v>
+        <v>1572.384833445934</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4066.940000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9238,28 +9910,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10604</v>
+        <v>3774</v>
       </c>
       <c r="E31" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="F31" t="n">
-        <v>573.79</v>
+        <v>1277.505166554066</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9271,28 +9943,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16261</v>
+        <v>610</v>
       </c>
       <c r="E32" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
-        <v>740.99</v>
+        <v>158.09</v>
       </c>
       <c r="G32" t="n">
-        <v>9235.59</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9304,28 +9976,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4909</v>
+        <v>610</v>
       </c>
       <c r="E33" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>502.2889268752047</v>
+        <v>158.09</v>
       </c>
       <c r="G33" t="n">
-        <v>3219.5</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -9337,28 +10009,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18925</v>
+        <v>610</v>
       </c>
       <c r="E34" t="n">
-        <v>237</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>1936.431073124795</v>
+        <v>158.09</v>
       </c>
       <c r="G34" t="n">
-        <v>12411.86</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9370,28 +10042,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>724</v>
+        <v>28986</v>
       </c>
       <c r="E35" t="n">
-        <v>46</v>
+        <v>295</v>
       </c>
       <c r="F35" t="n">
-        <v>579.7454791149779</v>
+        <v>3183.28</v>
       </c>
       <c r="G35" t="n">
-        <v>3324.664340316445</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9403,28 +10075,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4348</v>
+        <v>32287</v>
       </c>
       <c r="E36" t="n">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="F36" t="n">
-        <v>3479.047708985496</v>
+        <v>3614.42</v>
       </c>
       <c r="G36" t="n">
-        <v>19951.28254209249</v>
+        <v>10168.64</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9436,28 +10108,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10585</v>
+        <v>7950</v>
       </c>
       <c r="E37" t="n">
-        <v>667</v>
+        <v>90</v>
       </c>
       <c r="F37" t="n">
-        <v>8470.568850044219</v>
+        <v>1004.78</v>
       </c>
       <c r="G37" t="n">
-        <v>48576.14110407251</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9469,25 +10141,25 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>410</v>
+        <v>8341</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>150</v>
       </c>
       <c r="F38" t="n">
-        <v>328.437961855307</v>
+        <v>1562.07</v>
       </c>
       <c r="G38" t="n">
-        <v>1883.49201351856</v>
+        <v>5083.9</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -9502,22 +10174,22 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>9226</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="F39" t="n">
-        <v>6.59</v>
+        <v>1008.17</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9535,22 +10207,22 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>24</v>
+        <v>8979</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="F40" t="n">
-        <v>6.59</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -9568,28 +10240,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>24</v>
+        <v>11236</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="F41" t="n">
-        <v>6.59</v>
+        <v>1192.3</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -9601,22 +10273,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>311</v>
+        <v>16717</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="F42" t="n">
-        <v>43.68666666666667</v>
+        <v>960.66</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9634,28 +10306,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>311</v>
+        <v>25551</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="F43" t="n">
-        <v>43.68666666666667</v>
+        <v>1055.65</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>9235.59</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -9667,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>311</v>
+        <v>8043</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="F44" t="n">
-        <v>43.68666666666667</v>
+        <v>993.070229937643</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>6438.99</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -9700,28 +10372,28 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16041</v>
+        <v>6350</v>
       </c>
       <c r="E45" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F45" t="n">
-        <v>896.78</v>
+        <v>784.0778976174809</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -9733,28 +10405,28 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8476</v>
+        <v>15503</v>
       </c>
       <c r="E46" t="n">
-        <v>49</v>
+        <v>210</v>
       </c>
       <c r="F46" t="n">
-        <v>572.61</v>
+        <v>1914.251872444876</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>12411.86</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -9766,30 +10438,426 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>822</v>
+      </c>
+      <c r="E47" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" t="n">
+        <v>659.9957274352352</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3420.532190891349</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>6575</v>
+      </c>
+      <c r="E48" t="n">
+        <v>403</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5280.838359111231</v>
+      </c>
+      <c r="G48" t="n">
+        <v>27368.77960169272</v>
+      </c>
+      <c r="H48" t="n">
+        <v>8</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>15211</v>
+      </c>
+      <c r="E49" t="n">
+        <v>932</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12217.27132487589</v>
+      </c>
+      <c r="G49" t="n">
+        <v>63317.93997210768</v>
+      </c>
+      <c r="H49" t="n">
+        <v>19</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B0GLHC8CB3</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>466</v>
+      </c>
+      <c r="E50" t="n">
+        <v>29</v>
+      </c>
+      <c r="F50" t="n">
+        <v>373.9014090855015</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1937.8031596759</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B0GYS6CJD9</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>55</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="n">
+        <v>43.79317949214766</v>
+      </c>
+      <c r="G51" t="n">
+        <v>226.965075632362</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>27</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>27</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>27</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1316</v>
+      </c>
+      <c r="E55" t="n">
+        <v>33</v>
+      </c>
+      <c r="F55" t="n">
+        <v>379.16</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1987.29</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6745</v>
+      </c>
+      <c r="E56" t="n">
+        <v>40</v>
+      </c>
+      <c r="F56" t="n">
+        <v>429.1377866497453</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2880.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>19823</v>
+      </c>
+      <c r="E57" t="n">
+        <v>118</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1261.282213350255</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8466.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17292</v>
+      </c>
+      <c r="E58" t="n">
+        <v>116</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1369.61</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>125</v>
-      </c>
-      <c r="E47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="D59" t="n">
+        <v>187</v>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -2946,10 +2946,10 @@
         <v>104079</v>
       </c>
       <c r="G90" t="n">
-        <v>11692.38</v>
+        <v>16776.28</v>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9415,28 +9415,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14408</v>
+        <v>14042</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>247</v>
       </c>
       <c r="F16" t="n">
-        <v>625.7253013104111</v>
+        <v>2635.45</v>
       </c>
       <c r="G16" t="n">
-        <v>8808.975608171429</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9448,28 +9448,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9844</v>
+        <v>9645</v>
       </c>
       <c r="E17" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="F17" t="n">
-        <v>427.5446986895889</v>
+        <v>1598.452309254072</v>
       </c>
       <c r="G17" t="n">
-        <v>6018.984391828569</v>
+        <v>5057.64</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9481,28 +9481,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14042</v>
+        <v>3392</v>
       </c>
       <c r="E18" t="n">
-        <v>247</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>2635.45</v>
+        <v>562.187690745928</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1778.81</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9514,28 +9514,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9645</v>
+        <v>12966</v>
       </c>
       <c r="E19" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F19" t="n">
-        <v>1598.452309254072</v>
+        <v>1920.04</v>
       </c>
       <c r="G19" t="n">
-        <v>5057.64</v>
+        <v>2880.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9547,28 +9547,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3392</v>
+        <v>418</v>
       </c>
       <c r="E20" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
-        <v>562.187690745928</v>
+        <v>185.36</v>
       </c>
       <c r="G20" t="n">
-        <v>1778.81</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9580,28 +9580,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12966</v>
+        <v>418</v>
       </c>
       <c r="E21" t="n">
-        <v>170</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>1920.04</v>
+        <v>185.36</v>
       </c>
       <c r="G21" t="n">
-        <v>2880.5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9613,28 +9613,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2866</v>
+        <v>4437</v>
       </c>
       <c r="E22" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>350.6266666666667</v>
+        <v>589.86</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9646,22 +9646,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2866</v>
+        <v>25212</v>
       </c>
       <c r="E23" t="n">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="F23" t="n">
-        <v>350.6266666666667</v>
+        <v>2621.57</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9679,28 +9679,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2866</v>
+        <v>4645</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>350.6266666666667</v>
+        <v>1572.384833445934</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4066.940000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9712,28 +9712,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4348</v>
+        <v>3774</v>
       </c>
       <c r="E25" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>1038.49</v>
+        <v>1277.505166554066</v>
       </c>
       <c r="G25" t="n">
-        <v>5083.06</v>
+        <v>3304.24</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9745,22 +9745,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>418</v>
+        <v>28986</v>
       </c>
       <c r="E26" t="n">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="F26" t="n">
-        <v>185.36</v>
+        <v>3183.28</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9778,28 +9778,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>418</v>
+        <v>32287</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>308</v>
       </c>
       <c r="F27" t="n">
-        <v>185.36</v>
+        <v>3614.42</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>10168.64</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9811,28 +9811,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4437</v>
+        <v>7950</v>
       </c>
       <c r="E28" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F28" t="n">
-        <v>589.86</v>
+        <v>1004.78</v>
       </c>
       <c r="G28" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9844,28 +9844,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25212</v>
+        <v>8341</v>
       </c>
       <c r="E29" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F29" t="n">
-        <v>2621.57</v>
+        <v>1562.07</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9877,28 +9877,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4645</v>
+        <v>9226</v>
       </c>
       <c r="E30" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F30" t="n">
-        <v>1572.384833445934</v>
+        <v>1008.17</v>
       </c>
       <c r="G30" t="n">
-        <v>4066.940000000001</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9910,28 +9910,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3774</v>
+        <v>8979</v>
       </c>
       <c r="E31" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31" t="n">
-        <v>1277.505166554066</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9943,28 +9943,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>610</v>
+        <v>11236</v>
       </c>
       <c r="E32" t="n">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="F32" t="n">
-        <v>158.09</v>
+        <v>1192.3</v>
       </c>
       <c r="G32" t="n">
-        <v>777.6833333333334</v>
+        <v>5083.9</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9976,25 +9976,25 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>610</v>
+        <v>16717</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F33" t="n">
-        <v>158.09</v>
+        <v>960.66</v>
       </c>
       <c r="G33" t="n">
-        <v>777.6833333333334</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -10009,28 +10009,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>610</v>
+        <v>8043</v>
       </c>
       <c r="E34" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="F34" t="n">
-        <v>158.09</v>
+        <v>993.070229937643</v>
       </c>
       <c r="G34" t="n">
-        <v>777.6833333333334</v>
+        <v>6438.99</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -10042,28 +10042,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28986</v>
+        <v>6350</v>
       </c>
       <c r="E35" t="n">
-        <v>295</v>
+        <v>86</v>
       </c>
       <c r="F35" t="n">
-        <v>3183.28</v>
+        <v>784.0778976174809</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -10075,28 +10075,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32287</v>
+        <v>15503</v>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="F36" t="n">
-        <v>3614.42</v>
+        <v>1914.251872444876</v>
       </c>
       <c r="G36" t="n">
-        <v>10168.64</v>
+        <v>12411.86</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10108,28 +10108,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7950</v>
+        <v>822</v>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>1004.78</v>
+        <v>659.9957274352352</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3420.532190891349</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -10141,28 +10141,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8341</v>
+        <v>6575</v>
       </c>
       <c r="E38" t="n">
-        <v>150</v>
+        <v>403</v>
       </c>
       <c r="F38" t="n">
-        <v>1562.07</v>
+        <v>5280.838359111231</v>
       </c>
       <c r="G38" t="n">
-        <v>5083.9</v>
+        <v>27368.77960169272</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10174,28 +10174,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9226</v>
+        <v>15211</v>
       </c>
       <c r="E39" t="n">
-        <v>92</v>
+        <v>932</v>
       </c>
       <c r="F39" t="n">
-        <v>1008.17</v>
+        <v>12217.27132487589</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>63317.93997210768</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10207,28 +10207,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8979</v>
+        <v>466</v>
       </c>
       <c r="E40" t="n">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="F40" t="n">
-        <v>983.1600000000001</v>
+        <v>373.9014090855015</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1937.8031596759</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10240,28 +10240,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GYS6CJD9</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11236</v>
+        <v>55</v>
       </c>
       <c r="E41" t="n">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>1192.3</v>
+        <v>43.79317949214766</v>
       </c>
       <c r="G41" t="n">
-        <v>5083.9</v>
+        <v>226.965075632362</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10273,22 +10273,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16717</v>
+        <v>27</v>
       </c>
       <c r="E42" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>960.66</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -10306,28 +10306,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25551</v>
+        <v>27</v>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>1055.65</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G43" t="n">
-        <v>9235.59</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -10339,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8043</v>
+        <v>27</v>
       </c>
       <c r="E44" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>993.070229937643</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G44" t="n">
-        <v>6438.99</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10372,25 +10372,25 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6350</v>
+        <v>1316</v>
       </c>
       <c r="E45" t="n">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F45" t="n">
-        <v>784.0778976174809</v>
+        <v>379.16</v>
       </c>
       <c r="G45" t="n">
-        <v>5083.9</v>
+        <v>1987.29</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -10405,28 +10405,28 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15503</v>
+        <v>6745</v>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="F46" t="n">
-        <v>1914.251872444876</v>
+        <v>429.1377866497453</v>
       </c>
       <c r="G46" t="n">
-        <v>12411.86</v>
+        <v>2880.5</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10438,25 +10438,25 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>822</v>
+        <v>19823</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="F47" t="n">
-        <v>659.9957274352352</v>
+        <v>1261.282213350255</v>
       </c>
       <c r="G47" t="n">
-        <v>3420.532190891349</v>
+        <v>8466.1</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -10471,28 +10471,28 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6575</v>
+        <v>17292</v>
       </c>
       <c r="E48" t="n">
-        <v>403</v>
+        <v>116</v>
       </c>
       <c r="F48" t="n">
-        <v>5280.838359111231</v>
+        <v>1369.61</v>
       </c>
       <c r="G48" t="n">
-        <v>27368.77960169272</v>
+        <v>2880.51</v>
       </c>
       <c r="H48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10504,360 +10504,30 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15211</v>
+        <v>187</v>
       </c>
       <c r="E49" t="n">
-        <v>932</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>12217.27132487589</v>
+        <v>45.68</v>
       </c>
       <c r="G49" t="n">
-        <v>63317.93997210768</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>B0GLHC8CB3</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>466</v>
-      </c>
-      <c r="E50" t="n">
-        <v>29</v>
-      </c>
-      <c r="F50" t="n">
-        <v>373.9014090855015</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1937.8031596759</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>B0GYS6CJD9</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>55</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3</v>
-      </c>
-      <c r="F51" t="n">
-        <v>43.79317949214766</v>
-      </c>
-      <c r="G51" t="n">
-        <v>226.965075632362</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>B0CDPP45BM</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>27</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>27</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2</v>
-      </c>
-      <c r="F53" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>27</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2</v>
-      </c>
-      <c r="F54" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1316</v>
-      </c>
-      <c r="E55" t="n">
-        <v>33</v>
-      </c>
-      <c r="F55" t="n">
-        <v>379.16</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1987.29</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>6745</v>
-      </c>
-      <c r="E56" t="n">
-        <v>40</v>
-      </c>
-      <c r="F56" t="n">
-        <v>429.1377866497453</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2880.5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>19823</v>
-      </c>
-      <c r="E57" t="n">
-        <v>118</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1261.282213350255</v>
-      </c>
-      <c r="G57" t="n">
-        <v>8466.1</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>17292</v>
-      </c>
-      <c r="E58" t="n">
-        <v>116</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1369.61</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2880.51</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>187</v>
-      </c>
-      <c r="E59" t="n">
-        <v>5</v>
-      </c>
-      <c r="F59" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9415,28 +9415,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14042</v>
+        <v>14408</v>
       </c>
       <c r="E16" t="n">
-        <v>247</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>2635.45</v>
+        <v>625.7253013104111</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8808.975608171429</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9448,28 +9448,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9645</v>
+        <v>9844</v>
       </c>
       <c r="E17" t="n">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="F17" t="n">
-        <v>1598.452309254072</v>
+        <v>427.5446986895889</v>
       </c>
       <c r="G17" t="n">
-        <v>5057.64</v>
+        <v>6018.984391828569</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9481,28 +9481,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3392</v>
+        <v>14042</v>
       </c>
       <c r="E18" t="n">
-        <v>56</v>
+        <v>247</v>
       </c>
       <c r="F18" t="n">
-        <v>562.187690745928</v>
+        <v>2635.45</v>
       </c>
       <c r="G18" t="n">
-        <v>1778.81</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9514,28 +9514,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12966</v>
+        <v>9645</v>
       </c>
       <c r="E19" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>1920.04</v>
+        <v>1598.452309254072</v>
       </c>
       <c r="G19" t="n">
-        <v>2880.5</v>
+        <v>5057.64</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9547,28 +9547,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>418</v>
+        <v>3392</v>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F20" t="n">
-        <v>185.36</v>
+        <v>562.187690745928</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1778.81</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9580,28 +9580,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>418</v>
+        <v>12966</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="F21" t="n">
-        <v>185.36</v>
+        <v>1920.04</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2880.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9613,28 +9613,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4437</v>
+        <v>2866</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
-        <v>589.86</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9646,22 +9646,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25212</v>
+        <v>2866</v>
       </c>
       <c r="E23" t="n">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>2621.57</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9679,28 +9679,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4645</v>
+        <v>2866</v>
       </c>
       <c r="E24" t="n">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>1572.384833445934</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>4066.940000000001</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9712,28 +9712,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3774</v>
+        <v>4348</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>1277.505166554066</v>
+        <v>1038.49</v>
       </c>
       <c r="G25" t="n">
-        <v>3304.24</v>
+        <v>5083.06</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9745,22 +9745,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28986</v>
+        <v>418</v>
       </c>
       <c r="E26" t="n">
-        <v>295</v>
+        <v>13</v>
       </c>
       <c r="F26" t="n">
-        <v>3183.28</v>
+        <v>185.36</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9778,28 +9778,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>32287</v>
+        <v>418</v>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>3614.42</v>
+        <v>185.36</v>
       </c>
       <c r="G27" t="n">
-        <v>10168.64</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9811,28 +9811,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7950</v>
+        <v>4437</v>
       </c>
       <c r="E28" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>1004.78</v>
+        <v>589.86</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9844,28 +9844,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8341</v>
+        <v>25212</v>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F29" t="n">
-        <v>1562.07</v>
+        <v>2621.57</v>
       </c>
       <c r="G29" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9877,28 +9877,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9226</v>
+        <v>4645</v>
       </c>
       <c r="E30" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F30" t="n">
-        <v>1008.17</v>
+        <v>1572.384833445934</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4066.940000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9910,28 +9910,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8979</v>
+        <v>3774</v>
       </c>
       <c r="E31" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F31" t="n">
-        <v>983.1600000000001</v>
+        <v>1277.505166554066</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9943,28 +9943,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11236</v>
+        <v>610</v>
       </c>
       <c r="E32" t="n">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
-        <v>1192.3</v>
+        <v>158.09</v>
       </c>
       <c r="G32" t="n">
-        <v>5083.9</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9976,25 +9976,25 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16717</v>
+        <v>610</v>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>960.66</v>
+        <v>158.09</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -10009,28 +10009,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8043</v>
+        <v>610</v>
       </c>
       <c r="E34" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>993.070229937643</v>
+        <v>158.09</v>
       </c>
       <c r="G34" t="n">
-        <v>6438.99</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -10042,28 +10042,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6350</v>
+        <v>28986</v>
       </c>
       <c r="E35" t="n">
-        <v>86</v>
+        <v>295</v>
       </c>
       <c r="F35" t="n">
-        <v>784.0778976174809</v>
+        <v>3183.28</v>
       </c>
       <c r="G35" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -10075,28 +10075,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15503</v>
+        <v>32287</v>
       </c>
       <c r="E36" t="n">
-        <v>210</v>
+        <v>308</v>
       </c>
       <c r="F36" t="n">
-        <v>1914.251872444876</v>
+        <v>3614.42</v>
       </c>
       <c r="G36" t="n">
-        <v>12411.86</v>
+        <v>10168.64</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10108,28 +10108,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>822</v>
+        <v>7950</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F37" t="n">
-        <v>659.9957274352352</v>
+        <v>1004.78</v>
       </c>
       <c r="G37" t="n">
-        <v>3420.532190891349</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -10141,28 +10141,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6575</v>
+        <v>8341</v>
       </c>
       <c r="E38" t="n">
-        <v>403</v>
+        <v>150</v>
       </c>
       <c r="F38" t="n">
-        <v>5280.838359111231</v>
+        <v>1562.07</v>
       </c>
       <c r="G38" t="n">
-        <v>27368.77960169272</v>
+        <v>5083.9</v>
       </c>
       <c r="H38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10174,28 +10174,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15211</v>
+        <v>9226</v>
       </c>
       <c r="E39" t="n">
-        <v>932</v>
+        <v>92</v>
       </c>
       <c r="F39" t="n">
-        <v>12217.27132487589</v>
+        <v>1008.17</v>
       </c>
       <c r="G39" t="n">
-        <v>63317.93997210768</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10207,28 +10207,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>466</v>
+        <v>8979</v>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="F40" t="n">
-        <v>373.9014090855015</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>1937.8031596759</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10240,28 +10240,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>55</v>
+        <v>11236</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="F41" t="n">
-        <v>43.79317949214766</v>
+        <v>1192.3</v>
       </c>
       <c r="G41" t="n">
-        <v>226.965075632362</v>
+        <v>5083.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10273,22 +10273,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27</v>
+        <v>16717</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="F42" t="n">
-        <v>9.176666666666668</v>
+        <v>960.66</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -10306,28 +10306,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>27</v>
+        <v>25551</v>
       </c>
       <c r="E43" t="n">
+        <v>112</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1055.65</v>
+      </c>
+      <c r="G43" t="n">
+        <v>9235.59</v>
+      </c>
+      <c r="H43" t="n">
         <v>2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -10339,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27</v>
+        <v>8043</v>
       </c>
       <c r="E44" t="n">
+        <v>109</v>
+      </c>
+      <c r="F44" t="n">
+        <v>993.070229937643</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6438.99</v>
+      </c>
+      <c r="H44" t="n">
         <v>2</v>
-      </c>
-      <c r="F44" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10372,25 +10372,25 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1316</v>
+        <v>6350</v>
       </c>
       <c r="E45" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F45" t="n">
-        <v>379.16</v>
+        <v>784.0778976174809</v>
       </c>
       <c r="G45" t="n">
-        <v>1987.29</v>
+        <v>5083.9</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -10405,28 +10405,28 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6745</v>
+        <v>15503</v>
       </c>
       <c r="E46" t="n">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="F46" t="n">
-        <v>429.1377866497453</v>
+        <v>1914.251872444876</v>
       </c>
       <c r="G46" t="n">
-        <v>2880.5</v>
+        <v>12411.86</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10438,25 +10438,25 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>19823</v>
+        <v>822</v>
       </c>
       <c r="E47" t="n">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>1261.282213350255</v>
+        <v>659.9957274352352</v>
       </c>
       <c r="G47" t="n">
-        <v>8466.1</v>
+        <v>3420.532190891349</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -10471,28 +10471,28 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17292</v>
+        <v>6575</v>
       </c>
       <c r="E48" t="n">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F48" t="n">
-        <v>1369.61</v>
+        <v>5280.838359111231</v>
       </c>
       <c r="G48" t="n">
-        <v>2880.51</v>
+        <v>27368.77960169272</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10504,30 +10504,360 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>15211</v>
+      </c>
+      <c r="E49" t="n">
+        <v>932</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12217.27132487589</v>
+      </c>
+      <c r="G49" t="n">
+        <v>63317.93997210768</v>
+      </c>
+      <c r="H49" t="n">
+        <v>19</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B0GLHC8CB3</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>466</v>
+      </c>
+      <c r="E50" t="n">
+        <v>29</v>
+      </c>
+      <c r="F50" t="n">
+        <v>373.9014090855015</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1937.8031596759</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B0GYS6CJD9</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>55</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="n">
+        <v>43.79317949214766</v>
+      </c>
+      <c r="G51" t="n">
+        <v>226.965075632362</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>27</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>27</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>27</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1316</v>
+      </c>
+      <c r="E55" t="n">
+        <v>33</v>
+      </c>
+      <c r="F55" t="n">
+        <v>379.16</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1987.29</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6745</v>
+      </c>
+      <c r="E56" t="n">
+        <v>40</v>
+      </c>
+      <c r="F56" t="n">
+        <v>429.1377866497453</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2880.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>19823</v>
+      </c>
+      <c r="E57" t="n">
+        <v>118</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1261.282213350255</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8466.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17292</v>
+      </c>
+      <c r="E58" t="n">
+        <v>116</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1369.61</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D59" t="n">
         <v>187</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E59" t="n">
         <v>5</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F59" t="n">
         <v>45.68</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -9226,19 +9226,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>98</v>
+        <v>8119</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>127.61</v>
+        <v>2112.696666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2061.583333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -9259,19 +9259,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>98</v>
+        <v>8119</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>127.61</v>
+        <v>2112.696666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2061.583333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -9292,19 +9292,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24159</v>
+        <v>8119</v>
       </c>
       <c r="E12" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>6082.87</v>
+        <v>2112.696666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>6184.75</v>
+        <v>2061.583333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -9325,19 +9325,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63829</v>
+        <v>21276</v>
       </c>
       <c r="E13" t="n">
-        <v>373</v>
+        <v>124</v>
       </c>
       <c r="F13" t="n">
-        <v>6352.87</v>
+        <v>2117.623333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>17108.59</v>
+        <v>5702.863333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -9349,28 +9349,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9090</v>
+        <v>21276</v>
       </c>
       <c r="E14" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="F14" t="n">
-        <v>1110.916101265823</v>
+        <v>2117.623333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>4804.060886075949</v>
+        <v>5702.863333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -9382,28 +9382,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13779</v>
+        <v>21276</v>
       </c>
       <c r="E15" t="n">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="F15" t="n">
-        <v>1684.063898734177</v>
+        <v>2117.623333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>7282.58911392405</v>
+        <v>5702.863333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -9415,28 +9415,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14408</v>
+        <v>7623</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="F16" t="n">
-        <v>625.7253013104111</v>
+        <v>931.66</v>
       </c>
       <c r="G16" t="n">
-        <v>8808.975608171429</v>
+        <v>4028.883333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9448,28 +9448,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9844</v>
+        <v>7623</v>
       </c>
       <c r="E17" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="F17" t="n">
-        <v>427.5446986895889</v>
+        <v>931.66</v>
       </c>
       <c r="G17" t="n">
-        <v>6018.984391828569</v>
+        <v>4028.883333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9481,28 +9481,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14042</v>
+        <v>7623</v>
       </c>
       <c r="E18" t="n">
-        <v>247</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
-        <v>2635.45</v>
+        <v>931.66</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4028.883333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9514,25 +9514,25 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9645</v>
+        <v>14408</v>
       </c>
       <c r="E19" t="n">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="F19" t="n">
-        <v>1598.452309254072</v>
+        <v>625.7253013104111</v>
       </c>
       <c r="G19" t="n">
-        <v>5057.64</v>
+        <v>8808.975608171429</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
@@ -9547,25 +9547,25 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3392</v>
+        <v>9844</v>
       </c>
       <c r="E20" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F20" t="n">
-        <v>562.187690745928</v>
+        <v>427.5446986895889</v>
       </c>
       <c r="G20" t="n">
-        <v>1778.81</v>
+        <v>6018.984391828569</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -9580,28 +9580,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12966</v>
+        <v>14042</v>
       </c>
       <c r="E21" t="n">
-        <v>170</v>
+        <v>247</v>
       </c>
       <c r="F21" t="n">
-        <v>1920.04</v>
+        <v>2635.45</v>
       </c>
       <c r="G21" t="n">
-        <v>2880.5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9622,19 +9622,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2866</v>
+        <v>13037</v>
       </c>
       <c r="E22" t="n">
-        <v>31</v>
+        <v>216</v>
       </c>
       <c r="F22" t="n">
-        <v>350.6266666666667</v>
+        <v>2160.64</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>6836.450000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9646,28 +9646,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2866</v>
+        <v>12966</v>
       </c>
       <c r="E23" t="n">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="F23" t="n">
-        <v>350.6266666666667</v>
+        <v>1920.04</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2880.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9684,17 +9684,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2866</v>
+        <v>8598</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="F24" t="n">
-        <v>350.6266666666667</v>
+        <v>1051.88</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9882,23 +9882,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4645</v>
+        <v>8419</v>
       </c>
       <c r="E30" t="n">
-        <v>110</v>
+        <v>199</v>
       </c>
       <c r="F30" t="n">
-        <v>1572.384833445934</v>
+        <v>2849.89</v>
       </c>
       <c r="G30" t="n">
-        <v>4066.940000000001</v>
+        <v>7371.18</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9910,25 +9910,25 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3774</v>
+        <v>1830</v>
       </c>
       <c r="E31" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>1277.505166554066</v>
+        <v>474.27</v>
       </c>
       <c r="G31" t="n">
-        <v>3304.24</v>
+        <v>2333.05</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -9943,25 +9943,25 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>610</v>
+        <v>28986</v>
       </c>
       <c r="E32" t="n">
-        <v>16</v>
+        <v>295</v>
       </c>
       <c r="F32" t="n">
-        <v>158.09</v>
+        <v>3183.28</v>
       </c>
       <c r="G32" t="n">
-        <v>777.6833333333334</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -9976,28 +9976,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>610</v>
+        <v>32287</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>308</v>
       </c>
       <c r="F33" t="n">
-        <v>158.09</v>
+        <v>3614.42</v>
       </c>
       <c r="G33" t="n">
-        <v>777.6833333333334</v>
+        <v>10168.64</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -10009,25 +10009,25 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>610</v>
+        <v>7950</v>
       </c>
       <c r="E34" t="n">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="F34" t="n">
-        <v>158.09</v>
+        <v>1004.78</v>
       </c>
       <c r="G34" t="n">
-        <v>777.6833333333334</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -10042,7 +10042,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10051,19 +10051,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28986</v>
+        <v>8341</v>
       </c>
       <c r="E35" t="n">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="F35" t="n">
-        <v>3183.28</v>
+        <v>1562.07</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -10075,28 +10075,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32287</v>
+        <v>9226</v>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>92</v>
       </c>
       <c r="F36" t="n">
-        <v>3614.42</v>
+        <v>1008.17</v>
       </c>
       <c r="G36" t="n">
-        <v>10168.64</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10117,13 +10117,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7950</v>
+        <v>8979</v>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F37" t="n">
-        <v>1004.78</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -10141,7 +10141,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8341</v>
+        <v>11236</v>
       </c>
       <c r="E38" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="F38" t="n">
-        <v>1562.07</v>
+        <v>1192.3</v>
       </c>
       <c r="G38" t="n">
         <v>5083.9</v>
@@ -10174,7 +10174,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10183,13 +10183,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9226</v>
+        <v>16717</v>
       </c>
       <c r="E39" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="F39" t="n">
-        <v>1008.17</v>
+        <v>960.66</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -10207,28 +10207,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8979</v>
+        <v>25551</v>
       </c>
       <c r="E40" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="F40" t="n">
-        <v>983.1600000000001</v>
+        <v>1055.65</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>9235.59</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10240,28 +10240,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11236</v>
+        <v>9965</v>
       </c>
       <c r="E41" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F41" t="n">
-        <v>1192.3</v>
+        <v>1230.466666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>5083.9</v>
+        <v>7978.25</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10273,28 +10273,28 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16717</v>
+        <v>9965</v>
       </c>
       <c r="E42" t="n">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="F42" t="n">
-        <v>960.66</v>
+        <v>1230.466666666667</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>7978.25</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10306,25 +10306,25 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25551</v>
+        <v>9965</v>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F43" t="n">
-        <v>1055.65</v>
+        <v>1230.466666666667</v>
       </c>
       <c r="G43" t="n">
-        <v>9235.59</v>
+        <v>7978.25</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
@@ -10339,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8043</v>
+        <v>7709</v>
       </c>
       <c r="E44" t="n">
-        <v>109</v>
+        <v>472</v>
       </c>
       <c r="F44" t="n">
-        <v>993.070229937643</v>
+        <v>6191.933333333333</v>
       </c>
       <c r="G44" t="n">
-        <v>6438.99</v>
+        <v>32090.67333333334</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -10381,19 +10381,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6350</v>
+        <v>7709</v>
       </c>
       <c r="E45" t="n">
-        <v>86</v>
+        <v>472</v>
       </c>
       <c r="F45" t="n">
-        <v>784.0778976174809</v>
+        <v>6191.933333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>5083.9</v>
+        <v>32090.67333333334</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10414,19 +10414,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15503</v>
+        <v>7709</v>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>472</v>
       </c>
       <c r="F46" t="n">
-        <v>1914.251872444876</v>
+        <v>6191.933333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>12411.86</v>
+        <v>32090.67333333334</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10438,28 +10438,28 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>822</v>
+        <v>27</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>659.9957274352352</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G47" t="n">
-        <v>3420.532190891349</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10480,19 +10480,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6575</v>
+        <v>27</v>
       </c>
       <c r="E48" t="n">
-        <v>403</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>5280.838359111231</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G48" t="n">
-        <v>27368.77960169272</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10513,19 +10513,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15211</v>
+        <v>27</v>
       </c>
       <c r="E49" t="n">
-        <v>932</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>12217.27132487589</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G49" t="n">
-        <v>63317.93997210768</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -10537,28 +10537,28 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="E50" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F50" t="n">
-        <v>373.9014090855015</v>
+        <v>126.3866666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>1937.8031596759</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -10570,25 +10570,25 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>55</v>
+        <v>439</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F51" t="n">
-        <v>43.79317949214766</v>
+        <v>126.3866666666667</v>
       </c>
       <c r="G51" t="n">
-        <v>226.965075632362</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -10603,25 +10603,25 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>27</v>
+        <v>439</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F52" t="n">
-        <v>9.176666666666668</v>
+        <v>126.3866666666667</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -10636,28 +10636,28 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>27</v>
+        <v>26568</v>
       </c>
       <c r="E53" t="n">
+        <v>158</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1690.42</v>
+      </c>
+      <c r="G53" t="n">
+        <v>11346.6</v>
+      </c>
+      <c r="H53" t="n">
         <v>2</v>
-      </c>
-      <c r="F53" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10669,28 +10669,28 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>27</v>
+        <v>17292</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="F54" t="n">
-        <v>9.176666666666668</v>
+        <v>1369.61</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10702,162 +10702,30 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1316</v>
+        <v>187</v>
       </c>
       <c r="E55" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
-        <v>379.16</v>
+        <v>45.68</v>
       </c>
       <c r="G55" t="n">
-        <v>1987.29</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>6745</v>
-      </c>
-      <c r="E56" t="n">
-        <v>40</v>
-      </c>
-      <c r="F56" t="n">
-        <v>429.1377866497453</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2880.5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>19823</v>
-      </c>
-      <c r="E57" t="n">
-        <v>118</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1261.282213350255</v>
-      </c>
-      <c r="G57" t="n">
-        <v>8466.1</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>17292</v>
-      </c>
-      <c r="E58" t="n">
-        <v>116</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1369.61</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2880.51</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>187</v>
-      </c>
-      <c r="E59" t="n">
-        <v>5</v>
-      </c>
-      <c r="F59" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -6841,7 +6841,7 @@
         <v>66039.86</v>
       </c>
       <c r="H229" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="230">
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9433,7 +9433,7 @@
         <v>931.66</v>
       </c>
       <c r="G16" t="n">
-        <v>4028.883333333333</v>
+        <v>4377.773333333334</v>
       </c>
       <c r="H16" t="n">
         <v>3</v>
@@ -9466,7 +9466,7 @@
         <v>931.66</v>
       </c>
       <c r="G17" t="n">
-        <v>4028.883333333333</v>
+        <v>4377.773333333334</v>
       </c>
       <c r="H17" t="n">
         <v>3</v>
@@ -9499,7 +9499,7 @@
         <v>931.66</v>
       </c>
       <c r="G18" t="n">
-        <v>4028.883333333333</v>
+        <v>4377.773333333334</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
@@ -9688,13 +9688,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8598</v>
+        <v>2866</v>
       </c>
       <c r="E24" t="n">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>1051.88</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9712,28 +9712,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4348</v>
+        <v>2866</v>
       </c>
       <c r="E25" t="n">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>1038.49</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>5083.06</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9745,22 +9745,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>418</v>
+        <v>2866</v>
       </c>
       <c r="E26" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>185.36</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9778,28 +9778,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>418</v>
+        <v>4348</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="F27" t="n">
-        <v>185.36</v>
+        <v>1038.49</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>5083.06</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9811,28 +9811,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4437</v>
+        <v>418</v>
       </c>
       <c r="E28" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
-        <v>589.86</v>
+        <v>185.36</v>
       </c>
       <c r="G28" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9844,22 +9844,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25212</v>
+        <v>418</v>
       </c>
       <c r="E29" t="n">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
-        <v>2621.57</v>
+        <v>185.36</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -9877,7 +9877,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9886,19 +9886,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8419</v>
+        <v>4437</v>
       </c>
       <c r="E30" t="n">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="F30" t="n">
-        <v>2849.89</v>
+        <v>589.86</v>
       </c>
       <c r="G30" t="n">
-        <v>7371.18</v>
+        <v>5083.9</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9919,19 +9919,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1830</v>
+        <v>25212</v>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="F31" t="n">
-        <v>474.27</v>
+        <v>2621.57</v>
       </c>
       <c r="G31" t="n">
-        <v>2333.05</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9943,28 +9943,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28986</v>
+        <v>8419</v>
       </c>
       <c r="E32" t="n">
-        <v>295</v>
+        <v>199</v>
       </c>
       <c r="F32" t="n">
-        <v>3183.28</v>
+        <v>2849.89</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>7371.18</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9976,28 +9976,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>32287</v>
+        <v>610</v>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>3614.42</v>
+        <v>158.09</v>
       </c>
       <c r="G33" t="n">
-        <v>10168.64</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -10009,25 +10009,25 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7950</v>
+        <v>610</v>
       </c>
       <c r="E34" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>1004.78</v>
+        <v>158.09</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -10042,28 +10042,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8341</v>
+        <v>610</v>
       </c>
       <c r="E35" t="n">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>1562.07</v>
+        <v>158.09</v>
       </c>
       <c r="G35" t="n">
-        <v>5083.9</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10084,13 +10084,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9226</v>
+        <v>28986</v>
       </c>
       <c r="E36" t="n">
-        <v>92</v>
+        <v>295</v>
       </c>
       <c r="F36" t="n">
-        <v>1008.17</v>
+        <v>3183.28</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10117,19 +10117,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8979</v>
+        <v>32287</v>
       </c>
       <c r="E37" t="n">
-        <v>88</v>
+        <v>308</v>
       </c>
       <c r="F37" t="n">
-        <v>983.1600000000001</v>
+        <v>3614.42</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>10168.64</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10150,19 +10150,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11236</v>
+        <v>7950</v>
       </c>
       <c r="E38" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F38" t="n">
-        <v>1192.3</v>
+        <v>1004.78</v>
       </c>
       <c r="G38" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10183,19 +10183,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16717</v>
+        <v>8341</v>
       </c>
       <c r="E39" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="F39" t="n">
-        <v>960.66</v>
+        <v>1562.07</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10207,28 +10207,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25551</v>
+        <v>9226</v>
       </c>
       <c r="E40" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="F40" t="n">
-        <v>1055.65</v>
+        <v>1008.17</v>
       </c>
       <c r="G40" t="n">
-        <v>9235.59</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10240,28 +10240,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9965</v>
+        <v>8979</v>
       </c>
       <c r="E41" t="n">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="F41" t="n">
-        <v>1230.466666666667</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>7978.25</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10273,28 +10273,28 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9965</v>
+        <v>11236</v>
       </c>
       <c r="E42" t="n">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F42" t="n">
-        <v>1230.466666666667</v>
+        <v>1192.3</v>
       </c>
       <c r="G42" t="n">
-        <v>7978.25</v>
+        <v>5083.9</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10306,28 +10306,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9965</v>
+        <v>16717</v>
       </c>
       <c r="E43" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="F43" t="n">
-        <v>1230.466666666667</v>
+        <v>960.66</v>
       </c>
       <c r="G43" t="n">
-        <v>7978.25</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -10339,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7709</v>
+        <v>25551</v>
       </c>
       <c r="E44" t="n">
-        <v>472</v>
+        <v>112</v>
       </c>
       <c r="F44" t="n">
-        <v>6191.933333333333</v>
+        <v>1055.65</v>
       </c>
       <c r="G44" t="n">
-        <v>32090.67333333334</v>
+        <v>9235.59</v>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10372,28 +10372,28 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7709</v>
+        <v>9965</v>
       </c>
       <c r="E45" t="n">
-        <v>472</v>
+        <v>135</v>
       </c>
       <c r="F45" t="n">
-        <v>6191.933333333333</v>
+        <v>1230.466666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>32090.67333333334</v>
+        <v>7978.25</v>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -10405,28 +10405,28 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7709</v>
+        <v>9965</v>
       </c>
       <c r="E46" t="n">
-        <v>472</v>
+        <v>135</v>
       </c>
       <c r="F46" t="n">
-        <v>6191.933333333333</v>
+        <v>1230.466666666667</v>
       </c>
       <c r="G46" t="n">
-        <v>32090.67333333334</v>
+        <v>7978.25</v>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10438,28 +10438,28 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>27</v>
+        <v>9965</v>
       </c>
       <c r="E47" t="n">
+        <v>135</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1230.466666666667</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7978.25</v>
+      </c>
+      <c r="H47" t="n">
         <v>2</v>
-      </c>
-      <c r="F47" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -10471,28 +10471,28 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>27</v>
+        <v>7709</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>472</v>
       </c>
       <c r="F48" t="n">
-        <v>9.176666666666668</v>
+        <v>6191.933333333333</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>32090.67333333334</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10504,28 +10504,28 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>27</v>
+        <v>7709</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>472</v>
       </c>
       <c r="F49" t="n">
-        <v>9.176666666666668</v>
+        <v>6191.933333333333</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>32090.67333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -10537,28 +10537,28 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>439</v>
+        <v>7709</v>
       </c>
       <c r="E50" t="n">
-        <v>11</v>
+        <v>472</v>
       </c>
       <c r="F50" t="n">
-        <v>126.3866666666667</v>
+        <v>6191.933333333333</v>
       </c>
       <c r="G50" t="n">
-        <v>662.4299999999999</v>
+        <v>32090.67333333334</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -10570,25 +10570,25 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>439</v>
+        <v>27</v>
       </c>
       <c r="E51" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>126.3866666666667</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G51" t="n">
-        <v>662.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -10603,25 +10603,25 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>439</v>
+        <v>27</v>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>126.3866666666667</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G52" t="n">
-        <v>662.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -10636,28 +10636,28 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26568</v>
+        <v>27</v>
       </c>
       <c r="E53" t="n">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>1690.42</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G53" t="n">
-        <v>11346.6</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10669,28 +10669,28 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>17292</v>
+        <v>439</v>
       </c>
       <c r="E54" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="F54" t="n">
-        <v>1369.61</v>
+        <v>126.3866666666667</v>
       </c>
       <c r="G54" t="n">
-        <v>2880.51</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10702,30 +10702,162 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>439</v>
+      </c>
+      <c r="E55" t="n">
+        <v>11</v>
+      </c>
+      <c r="F55" t="n">
+        <v>126.3866666666667</v>
+      </c>
+      <c r="G55" t="n">
+        <v>662.4299999999999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>439</v>
+      </c>
+      <c r="E56" t="n">
+        <v>11</v>
+      </c>
+      <c r="F56" t="n">
+        <v>126.3866666666667</v>
+      </c>
+      <c r="G56" t="n">
+        <v>662.4299999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>26568</v>
+      </c>
+      <c r="E57" t="n">
+        <v>158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1690.42</v>
+      </c>
+      <c r="G57" t="n">
+        <v>11346.6</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17292</v>
+      </c>
+      <c r="E58" t="n">
+        <v>116</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1369.61</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D59" t="n">
         <v>187</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E59" t="n">
         <v>5</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F59" t="n">
         <v>45.68</v>
       </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -9226,19 +9226,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8119</v>
+        <v>98</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>2112.696666666667</v>
+        <v>127.61</v>
       </c>
       <c r="G10" t="n">
-        <v>2061.583333333333</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -9259,19 +9259,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8119</v>
+        <v>98</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>2112.696666666667</v>
+        <v>127.61</v>
       </c>
       <c r="G11" t="n">
-        <v>2061.583333333333</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -9292,19 +9292,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8119</v>
+        <v>24159</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="F12" t="n">
-        <v>2112.696666666667</v>
+        <v>6082.87</v>
       </c>
       <c r="G12" t="n">
-        <v>2061.583333333333</v>
+        <v>6184.75</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -9325,19 +9325,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21276</v>
+        <v>63829</v>
       </c>
       <c r="E13" t="n">
-        <v>124</v>
+        <v>373</v>
       </c>
       <c r="F13" t="n">
-        <v>2117.623333333333</v>
+        <v>6352.87</v>
       </c>
       <c r="G13" t="n">
-        <v>5702.863333333334</v>
+        <v>17108.59</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -9349,28 +9349,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21276</v>
+        <v>9090</v>
       </c>
       <c r="E14" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="F14" t="n">
-        <v>2117.623333333333</v>
+        <v>1110.916101265823</v>
       </c>
       <c r="G14" t="n">
-        <v>5702.863333333334</v>
+        <v>5220.079088607595</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -9382,28 +9382,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>21276</v>
+        <v>13779</v>
       </c>
       <c r="E15" t="n">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="F15" t="n">
-        <v>2117.623333333333</v>
+        <v>1684.063898734177</v>
       </c>
       <c r="G15" t="n">
-        <v>5702.863333333334</v>
+        <v>7913.240911392405</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -9415,28 +9415,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7623</v>
+        <v>14042</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>247</v>
       </c>
       <c r="F16" t="n">
-        <v>931.66</v>
+        <v>2635.45</v>
       </c>
       <c r="G16" t="n">
-        <v>4377.773333333334</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9448,28 +9448,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7623</v>
+        <v>9645</v>
       </c>
       <c r="E17" t="n">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="F17" t="n">
-        <v>931.66</v>
+        <v>1598.452309254072</v>
       </c>
       <c r="G17" t="n">
-        <v>4377.773333333334</v>
+        <v>5057.64</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9481,28 +9481,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7623</v>
+        <v>3392</v>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>931.66</v>
+        <v>562.187690745928</v>
       </c>
       <c r="G18" t="n">
-        <v>4377.773333333334</v>
+        <v>1778.81</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9514,28 +9514,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14408</v>
+        <v>12966</v>
       </c>
       <c r="E19" t="n">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="F19" t="n">
-        <v>625.7253013104111</v>
+        <v>1920.04</v>
       </c>
       <c r="G19" t="n">
-        <v>8808.975608171429</v>
+        <v>2880.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9547,28 +9547,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9844</v>
+        <v>418</v>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
-        <v>427.5446986895889</v>
+        <v>185.36</v>
       </c>
       <c r="G20" t="n">
-        <v>6018.984391828569</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9580,22 +9580,22 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14042</v>
+        <v>418</v>
       </c>
       <c r="E21" t="n">
-        <v>247</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>2635.45</v>
+        <v>185.36</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9613,28 +9613,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13037</v>
+        <v>4437</v>
       </c>
       <c r="E22" t="n">
-        <v>216</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>2160.64</v>
+        <v>589.86</v>
       </c>
       <c r="G22" t="n">
-        <v>6836.450000000001</v>
+        <v>5083.9</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9646,28 +9646,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12966</v>
+        <v>25212</v>
       </c>
       <c r="E23" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F23" t="n">
-        <v>1920.04</v>
+        <v>2621.57</v>
       </c>
       <c r="G23" t="n">
-        <v>2880.5</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9679,28 +9679,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2866</v>
+        <v>4645</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>350.6266666666667</v>
+        <v>1572.384833445934</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4066.940000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9712,28 +9712,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2866</v>
+        <v>3774</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="F25" t="n">
-        <v>350.6266666666667</v>
+        <v>1277.505166554066</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9745,22 +9745,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2866</v>
+        <v>28986</v>
       </c>
       <c r="E26" t="n">
-        <v>31</v>
+        <v>295</v>
       </c>
       <c r="F26" t="n">
-        <v>350.6266666666667</v>
+        <v>3183.28</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9778,28 +9778,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4348</v>
+        <v>32287</v>
       </c>
       <c r="E27" t="n">
-        <v>91</v>
+        <v>308</v>
       </c>
       <c r="F27" t="n">
-        <v>1038.49</v>
+        <v>3614.42</v>
       </c>
       <c r="G27" t="n">
-        <v>5083.06</v>
+        <v>10168.64</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9811,22 +9811,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>418</v>
+        <v>7950</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="F28" t="n">
-        <v>185.36</v>
+        <v>1004.78</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -9844,28 +9844,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>418</v>
+        <v>8341</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="F29" t="n">
-        <v>185.36</v>
+        <v>1562.07</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9877,28 +9877,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4437</v>
+        <v>9226</v>
       </c>
       <c r="E30" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="F30" t="n">
-        <v>589.86</v>
+        <v>1008.17</v>
       </c>
       <c r="G30" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9910,22 +9910,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25212</v>
+        <v>8979</v>
       </c>
       <c r="E31" t="n">
-        <v>200</v>
+        <v>88</v>
       </c>
       <c r="F31" t="n">
-        <v>2621.57</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -9943,28 +9943,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8419</v>
+        <v>11236</v>
       </c>
       <c r="E32" t="n">
-        <v>199</v>
+        <v>110</v>
       </c>
       <c r="F32" t="n">
-        <v>2849.89</v>
+        <v>1192.3</v>
       </c>
       <c r="G32" t="n">
-        <v>7371.18</v>
+        <v>5083.9</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9976,25 +9976,25 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>610</v>
+        <v>16717</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F33" t="n">
-        <v>158.09</v>
+        <v>960.66</v>
       </c>
       <c r="G33" t="n">
-        <v>777.6833333333334</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -10009,28 +10009,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>610</v>
+        <v>8043</v>
       </c>
       <c r="E34" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="F34" t="n">
-        <v>158.09</v>
+        <v>993.070229937643</v>
       </c>
       <c r="G34" t="n">
-        <v>777.6833333333334</v>
+        <v>6438.99</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -10042,28 +10042,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>610</v>
+        <v>6350</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="F35" t="n">
-        <v>158.09</v>
+        <v>784.0778976174809</v>
       </c>
       <c r="G35" t="n">
-        <v>777.6833333333334</v>
+        <v>5083.9</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -10075,28 +10075,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28986</v>
+        <v>15503</v>
       </c>
       <c r="E36" t="n">
-        <v>295</v>
+        <v>210</v>
       </c>
       <c r="F36" t="n">
-        <v>3183.28</v>
+        <v>1914.251872444876</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>12411.86</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10108,25 +10108,25 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>32287</v>
+        <v>822</v>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>3614.42</v>
+        <v>659.9957274352352</v>
       </c>
       <c r="G37" t="n">
-        <v>10168.64</v>
+        <v>3420.532190891349</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -10141,28 +10141,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7950</v>
+        <v>6575</v>
       </c>
       <c r="E38" t="n">
-        <v>90</v>
+        <v>403</v>
       </c>
       <c r="F38" t="n">
-        <v>1004.78</v>
+        <v>5280.838359111231</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>27368.77960169272</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10174,28 +10174,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8341</v>
+        <v>15211</v>
       </c>
       <c r="E39" t="n">
-        <v>150</v>
+        <v>932</v>
       </c>
       <c r="F39" t="n">
-        <v>1562.07</v>
+        <v>12217.27132487589</v>
       </c>
       <c r="G39" t="n">
-        <v>5083.9</v>
+        <v>63317.93997210768</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10207,28 +10207,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9226</v>
+        <v>466</v>
       </c>
       <c r="E40" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="F40" t="n">
-        <v>1008.17</v>
+        <v>373.9014090855015</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1937.8031596759</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10240,25 +10240,25 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GYS6CJD9</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8979</v>
+        <v>55</v>
       </c>
       <c r="E41" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>983.1600000000001</v>
+        <v>43.79317949214766</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>226.965075632362</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -10273,28 +10273,28 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11236</v>
+        <v>27</v>
       </c>
       <c r="E42" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>1192.3</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G42" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10306,22 +10306,22 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16717</v>
+        <v>27</v>
       </c>
       <c r="E43" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>960.66</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -10339,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25551</v>
+        <v>27</v>
       </c>
       <c r="E44" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>1055.65</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G44" t="n">
-        <v>9235.59</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10372,28 +10372,28 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9965</v>
+        <v>1316</v>
       </c>
       <c r="E45" t="n">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="F45" t="n">
-        <v>1230.466666666667</v>
+        <v>379.16</v>
       </c>
       <c r="G45" t="n">
-        <v>7978.25</v>
+        <v>1987.29</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -10405,28 +10405,28 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9965</v>
+        <v>6745</v>
       </c>
       <c r="E46" t="n">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="F46" t="n">
-        <v>1230.466666666667</v>
+        <v>429.1377866497453</v>
       </c>
       <c r="G46" t="n">
-        <v>7978.25</v>
+        <v>2880.5</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10438,28 +10438,28 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9965</v>
+        <v>19823</v>
       </c>
       <c r="E47" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="F47" t="n">
-        <v>1230.466666666667</v>
+        <v>1261.282213350255</v>
       </c>
       <c r="G47" t="n">
-        <v>7978.25</v>
+        <v>8466.1</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -10471,28 +10471,28 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7709</v>
+        <v>17292</v>
       </c>
       <c r="E48" t="n">
-        <v>472</v>
+        <v>116</v>
       </c>
       <c r="F48" t="n">
-        <v>6191.933333333333</v>
+        <v>1369.61</v>
       </c>
       <c r="G48" t="n">
-        <v>32090.67333333334</v>
+        <v>2880.51</v>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10504,360 +10504,30 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7709</v>
+        <v>187</v>
       </c>
       <c r="E49" t="n">
-        <v>472</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>6191.933333333333</v>
+        <v>45.68</v>
       </c>
       <c r="G49" t="n">
-        <v>32090.67333333334</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>7709</v>
-      </c>
-      <c r="E50" t="n">
-        <v>472</v>
-      </c>
-      <c r="F50" t="n">
-        <v>6191.933333333333</v>
-      </c>
-      <c r="G50" t="n">
-        <v>32090.67333333334</v>
-      </c>
-      <c r="H50" t="n">
-        <v>10</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>B0CDPP45BM</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>27</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2</v>
-      </c>
-      <c r="F51" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>27</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>27</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2</v>
-      </c>
-      <c r="F53" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>439</v>
-      </c>
-      <c r="E54" t="n">
-        <v>11</v>
-      </c>
-      <c r="F54" t="n">
-        <v>126.3866666666667</v>
-      </c>
-      <c r="G54" t="n">
-        <v>662.4299999999999</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>439</v>
-      </c>
-      <c r="E55" t="n">
-        <v>11</v>
-      </c>
-      <c r="F55" t="n">
-        <v>126.3866666666667</v>
-      </c>
-      <c r="G55" t="n">
-        <v>662.4299999999999</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>439</v>
-      </c>
-      <c r="E56" t="n">
-        <v>11</v>
-      </c>
-      <c r="F56" t="n">
-        <v>126.3866666666667</v>
-      </c>
-      <c r="G56" t="n">
-        <v>662.4299999999999</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>26568</v>
-      </c>
-      <c r="E57" t="n">
-        <v>158</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1690.42</v>
-      </c>
-      <c r="G57" t="n">
-        <v>11346.6</v>
-      </c>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>17292</v>
-      </c>
-      <c r="E58" t="n">
-        <v>116</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1369.61</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2880.51</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>187</v>
-      </c>
-      <c r="E59" t="n">
-        <v>5</v>
-      </c>
-      <c r="F59" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -8546,10 +8546,10 @@
         <v>8959</v>
       </c>
       <c r="G43" t="n">
-        <v>5083.9</v>
+        <v>10167.8</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9415,28 +9415,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14042</v>
+        <v>14408</v>
       </c>
       <c r="E16" t="n">
-        <v>247</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>2635.45</v>
+        <v>625.7253013104111</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8808.975608171429</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9448,28 +9448,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9645</v>
+        <v>9844</v>
       </c>
       <c r="E17" t="n">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="F17" t="n">
-        <v>1598.452309254072</v>
+        <v>427.5446986895889</v>
       </c>
       <c r="G17" t="n">
-        <v>5057.64</v>
+        <v>6018.984391828569</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9481,28 +9481,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3392</v>
+        <v>14042</v>
       </c>
       <c r="E18" t="n">
-        <v>56</v>
+        <v>247</v>
       </c>
       <c r="F18" t="n">
-        <v>562.187690745928</v>
+        <v>2635.45</v>
       </c>
       <c r="G18" t="n">
-        <v>1778.81</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9514,28 +9514,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12966</v>
+        <v>9645</v>
       </c>
       <c r="E19" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>1920.04</v>
+        <v>1598.452309254072</v>
       </c>
       <c r="G19" t="n">
-        <v>2880.5</v>
+        <v>5057.64</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9547,28 +9547,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>418</v>
+        <v>3392</v>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F20" t="n">
-        <v>185.36</v>
+        <v>562.187690745928</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1778.81</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9580,28 +9580,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>418</v>
+        <v>12966</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="F21" t="n">
-        <v>185.36</v>
+        <v>1920.04</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2880.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9613,28 +9613,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4437</v>
+        <v>2866</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
-        <v>589.86</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9646,22 +9646,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25212</v>
+        <v>2866</v>
       </c>
       <c r="E23" t="n">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>2621.57</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9679,28 +9679,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4645</v>
+        <v>2866</v>
       </c>
       <c r="E24" t="n">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>1572.384833445934</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>4066.940000000001</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9712,28 +9712,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3774</v>
+        <v>4348</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>1277.505166554066</v>
+        <v>1038.49</v>
       </c>
       <c r="G25" t="n">
-        <v>3304.24</v>
+        <v>5083.06</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9745,22 +9745,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28986</v>
+        <v>418</v>
       </c>
       <c r="E26" t="n">
-        <v>295</v>
+        <v>13</v>
       </c>
       <c r="F26" t="n">
-        <v>3183.28</v>
+        <v>185.36</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9778,28 +9778,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>32287</v>
+        <v>418</v>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>3614.42</v>
+        <v>185.36</v>
       </c>
       <c r="G27" t="n">
-        <v>10168.64</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9811,28 +9811,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7950</v>
+        <v>4437</v>
       </c>
       <c r="E28" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>1004.78</v>
+        <v>589.86</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9844,28 +9844,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8341</v>
+        <v>25212</v>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F29" t="n">
-        <v>1562.07</v>
+        <v>2621.57</v>
       </c>
       <c r="G29" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9877,28 +9877,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9226</v>
+        <v>4645</v>
       </c>
       <c r="E30" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F30" t="n">
-        <v>1008.17</v>
+        <v>1572.384833445934</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4066.940000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9910,28 +9910,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8979</v>
+        <v>3774</v>
       </c>
       <c r="E31" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F31" t="n">
-        <v>983.1600000000001</v>
+        <v>1277.505166554066</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9943,28 +9943,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11236</v>
+        <v>610</v>
       </c>
       <c r="E32" t="n">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
-        <v>1192.3</v>
+        <v>158.09</v>
       </c>
       <c r="G32" t="n">
-        <v>5083.9</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9976,25 +9976,25 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16717</v>
+        <v>610</v>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>960.66</v>
+        <v>158.09</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -10009,28 +10009,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8043</v>
+        <v>610</v>
       </c>
       <c r="E34" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>993.070229937643</v>
+        <v>158.09</v>
       </c>
       <c r="G34" t="n">
-        <v>6438.99</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -10042,28 +10042,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6350</v>
+        <v>28986</v>
       </c>
       <c r="E35" t="n">
-        <v>86</v>
+        <v>295</v>
       </c>
       <c r="F35" t="n">
-        <v>784.0778976174809</v>
+        <v>3183.28</v>
       </c>
       <c r="G35" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -10075,28 +10075,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15503</v>
+        <v>32287</v>
       </c>
       <c r="E36" t="n">
-        <v>210</v>
+        <v>308</v>
       </c>
       <c r="F36" t="n">
-        <v>1914.251872444876</v>
+        <v>3614.42</v>
       </c>
       <c r="G36" t="n">
-        <v>12411.86</v>
+        <v>10168.64</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10108,28 +10108,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>822</v>
+        <v>7950</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F37" t="n">
-        <v>659.9957274352352</v>
+        <v>1004.78</v>
       </c>
       <c r="G37" t="n">
-        <v>3420.532190891349</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -10141,28 +10141,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6575</v>
+        <v>8341</v>
       </c>
       <c r="E38" t="n">
-        <v>403</v>
+        <v>150</v>
       </c>
       <c r="F38" t="n">
-        <v>5280.838359111231</v>
+        <v>1562.07</v>
       </c>
       <c r="G38" t="n">
-        <v>27368.77960169272</v>
+        <v>5083.9</v>
       </c>
       <c r="H38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10174,28 +10174,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15211</v>
+        <v>9226</v>
       </c>
       <c r="E39" t="n">
-        <v>932</v>
+        <v>92</v>
       </c>
       <c r="F39" t="n">
-        <v>12217.27132487589</v>
+        <v>1008.17</v>
       </c>
       <c r="G39" t="n">
-        <v>63317.93997210768</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10207,28 +10207,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>466</v>
+        <v>8979</v>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="F40" t="n">
-        <v>373.9014090855015</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>1937.8031596759</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10240,28 +10240,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>55</v>
+        <v>11236</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="F41" t="n">
-        <v>43.79317949214766</v>
+        <v>1192.3</v>
       </c>
       <c r="G41" t="n">
-        <v>226.965075632362</v>
+        <v>5083.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10273,22 +10273,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27</v>
+        <v>16717</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="F42" t="n">
-        <v>9.176666666666668</v>
+        <v>960.66</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -10306,28 +10306,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>27</v>
+        <v>25551</v>
       </c>
       <c r="E43" t="n">
+        <v>112</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1055.65</v>
+      </c>
+      <c r="G43" t="n">
+        <v>9235.59</v>
+      </c>
+      <c r="H43" t="n">
         <v>2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -10339,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27</v>
+        <v>8043</v>
       </c>
       <c r="E44" t="n">
+        <v>109</v>
+      </c>
+      <c r="F44" t="n">
+        <v>993.070229937643</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6438.99</v>
+      </c>
+      <c r="H44" t="n">
         <v>2</v>
-      </c>
-      <c r="F44" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10372,25 +10372,25 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1316</v>
+        <v>6350</v>
       </c>
       <c r="E45" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F45" t="n">
-        <v>379.16</v>
+        <v>784.0778976174809</v>
       </c>
       <c r="G45" t="n">
-        <v>1987.29</v>
+        <v>5083.9</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -10405,28 +10405,28 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6745</v>
+        <v>15503</v>
       </c>
       <c r="E46" t="n">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="F46" t="n">
-        <v>429.1377866497453</v>
+        <v>1914.251872444876</v>
       </c>
       <c r="G46" t="n">
-        <v>2880.5</v>
+        <v>12411.86</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10438,25 +10438,25 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>19823</v>
+        <v>822</v>
       </c>
       <c r="E47" t="n">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>1261.282213350255</v>
+        <v>659.9957274352352</v>
       </c>
       <c r="G47" t="n">
-        <v>8466.1</v>
+        <v>3420.532190891349</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -10471,28 +10471,28 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17292</v>
+        <v>6575</v>
       </c>
       <c r="E48" t="n">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F48" t="n">
-        <v>1369.61</v>
+        <v>5280.838359111231</v>
       </c>
       <c r="G48" t="n">
-        <v>2880.51</v>
+        <v>27368.77960169272</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10504,30 +10504,360 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>15211</v>
+      </c>
+      <c r="E49" t="n">
+        <v>932</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12217.27132487589</v>
+      </c>
+      <c r="G49" t="n">
+        <v>63317.93997210768</v>
+      </c>
+      <c r="H49" t="n">
+        <v>19</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B0GLHC8CB3</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>466</v>
+      </c>
+      <c r="E50" t="n">
+        <v>29</v>
+      </c>
+      <c r="F50" t="n">
+        <v>373.9014090855015</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1937.8031596759</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B0GYS6CJD9</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>55</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="n">
+        <v>43.79317949214766</v>
+      </c>
+      <c r="G51" t="n">
+        <v>226.965075632362</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>27</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>27</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>27</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9.176666666666668</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1316</v>
+      </c>
+      <c r="E55" t="n">
+        <v>33</v>
+      </c>
+      <c r="F55" t="n">
+        <v>379.16</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1987.29</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6745</v>
+      </c>
+      <c r="E56" t="n">
+        <v>40</v>
+      </c>
+      <c r="F56" t="n">
+        <v>429.1377866497453</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2880.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>19823</v>
+      </c>
+      <c r="E57" t="n">
+        <v>118</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1261.282213350255</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8466.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17292</v>
+      </c>
+      <c r="E58" t="n">
+        <v>116</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1369.61</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5761.02</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D59" t="n">
         <v>187</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E59" t="n">
         <v>5</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F59" t="n">
         <v>45.68</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -2915,7 +2915,7 @@
         <v>275</v>
       </c>
       <c r="F89" t="n">
-        <v>35900</v>
+        <v>35899</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>1265</v>
       </c>
       <c r="F98" t="n">
-        <v>678723</v>
+        <v>678721</v>
       </c>
       <c r="G98" t="n">
         <v>30503.4</v>
@@ -9334,10 +9334,10 @@
         <v>6352.87</v>
       </c>
       <c r="G13" t="n">
-        <v>17108.59</v>
+        <v>19964.78</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>1110.916101265823</v>
       </c>
       <c r="G14" t="n">
-        <v>5220.079088607595</v>
+        <v>4804.064860759494</v>
       </c>
       <c r="H14" t="n">
         <v>4</v>
@@ -9400,10 +9400,10 @@
         <v>1684.063898734177</v>
       </c>
       <c r="G15" t="n">
-        <v>7913.240911392405</v>
+        <v>7282.595139240506</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -731,7 +731,7 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>12226</v>
+        <v>12225</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
         <v>326</v>
       </c>
       <c r="F20" t="n">
-        <v>72126</v>
+        <v>72111</v>
       </c>
       <c r="G20" t="n">
         <v>20420.34</v>
@@ -1011,7 +1011,7 @@
         <v>430</v>
       </c>
       <c r="F21" t="n">
-        <v>30642</v>
+        <v>30638</v>
       </c>
       <c r="G21" t="n">
         <v>20335.6</v>
@@ -1039,7 +1039,7 @@
         <v>174</v>
       </c>
       <c r="F22" t="n">
-        <v>16025</v>
+        <v>16019</v>
       </c>
       <c r="G22" t="n">
         <v>15251.7</v>
@@ -1123,7 +1123,7 @@
         <v>418</v>
       </c>
       <c r="F25" t="n">
-        <v>155438</v>
+        <v>155436</v>
       </c>
       <c r="G25" t="n">
         <v>14739.85</v>
@@ -1151,7 +1151,7 @@
         <v>274</v>
       </c>
       <c r="F26" t="n">
-        <v>56003</v>
+        <v>56001</v>
       </c>
       <c r="G26" t="n">
         <v>10589</v>
@@ -1179,7 +1179,7 @@
         <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>21842</v>
+        <v>21840</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>37</v>
       </c>
       <c r="F32" t="n">
-        <v>8495</v>
+        <v>8493</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>52</v>
       </c>
       <c r="F35" t="n">
-        <v>16792</v>
+        <v>16789</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>152</v>
       </c>
       <c r="F42" t="n">
-        <v>5567</v>
+        <v>5565</v>
       </c>
       <c r="G42" t="n">
         <v>5083.06</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
         <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>423</v>
       </c>
       <c r="F62" t="n">
-        <v>13934</v>
+        <v>13931</v>
       </c>
       <c r="G62" t="n">
         <v>12789.86</v>
@@ -2243,7 +2243,7 @@
         <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>45</v>
       </c>
       <c r="F66" t="n">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>12</v>
       </c>
       <c r="F67" t="n">
-        <v>4546</v>
+        <v>4542</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>76</v>
       </c>
       <c r="F69" t="n">
-        <v>15195</v>
+        <v>15193</v>
       </c>
       <c r="G69" t="n">
         <v>2093.33</v>
@@ -2411,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
         <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>9465</v>
+        <v>9457</v>
       </c>
       <c r="G72" t="n">
         <v>1651.69</v>
@@ -2467,7 +2467,7 @@
         <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>176</v>
       </c>
       <c r="F88" t="n">
-        <v>28686</v>
+        <v>28684</v>
       </c>
       <c r="G88" t="n">
         <v>6853.34</v>
@@ -2971,7 +2971,7 @@
         <v>486</v>
       </c>
       <c r="F91" t="n">
-        <v>38733</v>
+        <v>38730</v>
       </c>
       <c r="G91" t="n">
         <v>35587.3</v>
@@ -3055,7 +3055,7 @@
         <v>177</v>
       </c>
       <c r="F94" t="n">
-        <v>22293</v>
+        <v>22292</v>
       </c>
       <c r="G94" t="n">
         <v>6945.76</v>
@@ -3086,10 +3086,10 @@
         <v>96181</v>
       </c>
       <c r="G95" t="n">
-        <v>12155.08</v>
+        <v>13891.52</v>
       </c>
       <c r="H95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
@@ -3111,7 +3111,7 @@
         <v>5</v>
       </c>
       <c r="F96" t="n">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>1265</v>
       </c>
       <c r="F98" t="n">
-        <v>678721</v>
+        <v>678704</v>
       </c>
       <c r="G98" t="n">
         <v>30503.4</v>
@@ -3195,7 +3195,7 @@
         <v>332</v>
       </c>
       <c r="F99" t="n">
-        <v>77544</v>
+        <v>77543</v>
       </c>
       <c r="G99" t="n">
         <v>15251.7</v>
@@ -3363,7 +3363,7 @@
         <v>425</v>
       </c>
       <c r="F105" t="n">
-        <v>138933</v>
+        <v>138899</v>
       </c>
       <c r="G105" t="n">
         <v>16603.4</v>
@@ -3391,7 +3391,7 @@
         <v>108</v>
       </c>
       <c r="F106" t="n">
-        <v>6586</v>
+        <v>6585</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>95</v>
       </c>
       <c r="F108" t="n">
-        <v>5881</v>
+        <v>5877</v>
       </c>
       <c r="G108" t="n">
         <v>8466.1</v>
@@ -3475,7 +3475,7 @@
         <v>113</v>
       </c>
       <c r="F109" t="n">
-        <v>13584</v>
+        <v>13581</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>20</v>
       </c>
       <c r="F120" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4007,7 +4007,7 @@
         <v>3</v>
       </c>
       <c r="F128" t="n">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -4203,7 +4203,7 @@
         <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>2396</v>
+        <v>2385</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>10</v>
       </c>
       <c r="F138" t="n">
-        <v>2403</v>
+        <v>2389</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
         <v>42</v>
       </c>
       <c r="F140" t="n">
-        <v>8679</v>
+        <v>8663</v>
       </c>
       <c r="G140" t="n">
         <v>8466.1</v>
@@ -4371,7 +4371,7 @@
         <v>25</v>
       </c>
       <c r="F141" t="n">
-        <v>9746</v>
+        <v>9719</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>5</v>
       </c>
       <c r="F142" t="n">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
         <v>11</v>
       </c>
       <c r="F148" t="n">
-        <v>6441</v>
+        <v>6439</v>
       </c>
       <c r="G148" t="n">
         <v>761.86</v>
@@ -4651,7 +4651,7 @@
         <v>79</v>
       </c>
       <c r="F151" t="n">
-        <v>20415</v>
+        <v>20413</v>
       </c>
       <c r="G151" t="n">
         <v>6606.78</v>
@@ -5015,7 +5015,7 @@
         <v>44</v>
       </c>
       <c r="F164" t="n">
-        <v>23129</v>
+        <v>23123</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
         <v>5</v>
       </c>
       <c r="F173" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G173" t="n">
         <v>12540.68</v>
@@ -5519,7 +5519,7 @@
         <v>97</v>
       </c>
       <c r="F182" t="n">
-        <v>12280</v>
+        <v>12278</v>
       </c>
       <c r="G182" t="n">
         <v>8466.1</v>
@@ -6247,7 +6247,7 @@
         <v>180</v>
       </c>
       <c r="F208" t="n">
-        <v>20348</v>
+        <v>20343</v>
       </c>
       <c r="G208" t="n">
         <v>12962.71</v>
@@ -6303,7 +6303,7 @@
         <v>142</v>
       </c>
       <c r="F210" t="n">
-        <v>45811</v>
+        <v>45808</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -6331,7 +6331,7 @@
         <v>1163</v>
       </c>
       <c r="F211" t="n">
-        <v>295820</v>
+        <v>295815</v>
       </c>
       <c r="G211" t="n">
         <v>21345.74</v>
@@ -6639,7 +6639,7 @@
         <v>161</v>
       </c>
       <c r="F222" t="n">
-        <v>17160</v>
+        <v>17158</v>
       </c>
       <c r="G222" t="n">
         <v>5083.06</v>
@@ -6807,7 +6807,7 @@
         <v>37</v>
       </c>
       <c r="F228" t="n">
-        <v>10209</v>
+        <v>10205</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6835,7 +6835,7 @@
         <v>477</v>
       </c>
       <c r="F229" t="n">
-        <v>114212</v>
+        <v>114207</v>
       </c>
       <c r="G229" t="n">
         <v>66039.86</v>
@@ -7171,7 +7171,7 @@
         <v>342</v>
       </c>
       <c r="F241" t="n">
-        <v>140768</v>
+        <v>140766</v>
       </c>
       <c r="G241" t="n">
         <v>8015.26</v>
@@ -7199,7 +7199,7 @@
         <v>90</v>
       </c>
       <c r="F242" t="n">
-        <v>13872</v>
+        <v>13871</v>
       </c>
       <c r="G242" t="n">
         <v>11900</v>
@@ -8543,7 +8543,7 @@
         <v>37</v>
       </c>
       <c r="F43" t="n">
-        <v>8959</v>
+        <v>8958</v>
       </c>
       <c r="G43" t="n">
         <v>10167.8</v>
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7805</v>
+        <v>7804</v>
       </c>
       <c r="E2" t="n">
         <v>161</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63829</v>
+        <v>63820</v>
       </c>
       <c r="E13" t="n">
         <v>373</v>
@@ -9420,23 +9420,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14408</v>
+        <v>8084</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
-        <v>625.7253013104111</v>
+        <v>351.09</v>
       </c>
       <c r="G16" t="n">
-        <v>8808.975608171429</v>
+        <v>4942.653333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9453,20 +9453,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9844</v>
+        <v>8084</v>
       </c>
       <c r="E17" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>427.5446986895889</v>
+        <v>351.09</v>
       </c>
       <c r="G17" t="n">
-        <v>6018.984391828569</v>
+        <v>4942.653333333333</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -9481,28 +9481,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14042</v>
+        <v>8084</v>
       </c>
       <c r="E18" t="n">
-        <v>247</v>
+        <v>31</v>
       </c>
       <c r="F18" t="n">
-        <v>2635.45</v>
+        <v>351.09</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4942.653333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9523,19 +9523,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9645</v>
+        <v>14042</v>
       </c>
       <c r="E19" t="n">
-        <v>160</v>
+        <v>247</v>
       </c>
       <c r="F19" t="n">
-        <v>1598.452309254072</v>
+        <v>2635.45</v>
       </c>
       <c r="G19" t="n">
-        <v>5057.64</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9552,23 +9552,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3392</v>
+        <v>9644</v>
       </c>
       <c r="E20" t="n">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="F20" t="n">
-        <v>562.187690745928</v>
+        <v>1598.452309254072</v>
       </c>
       <c r="G20" t="n">
-        <v>1778.81</v>
+        <v>5057.64</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9580,25 +9580,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12966</v>
+        <v>3392</v>
       </c>
       <c r="E21" t="n">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="F21" t="n">
-        <v>1920.04</v>
+        <v>562.187690745928</v>
       </c>
       <c r="G21" t="n">
-        <v>2880.5</v>
+        <v>1778.81</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -9613,28 +9613,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2866</v>
+        <v>12966</v>
       </c>
       <c r="E22" t="n">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="F22" t="n">
-        <v>350.6266666666667</v>
+        <v>1920.04</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2880.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -9712,28 +9712,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4348</v>
+        <v>2866</v>
       </c>
       <c r="E25" t="n">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>1038.49</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>5083.06</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9745,28 +9745,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>418</v>
+        <v>4348</v>
       </c>
       <c r="E26" t="n">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>185.36</v>
+        <v>1038.49</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5083.06</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -9811,28 +9811,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4437</v>
+        <v>418</v>
       </c>
       <c r="E28" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
-        <v>589.86</v>
+        <v>185.36</v>
       </c>
       <c r="G28" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9853,19 +9853,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25212</v>
+        <v>4433</v>
       </c>
       <c r="E29" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>2621.57</v>
+        <v>589.86</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9877,28 +9877,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4645</v>
+        <v>25205</v>
       </c>
       <c r="E30" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="F30" t="n">
-        <v>1572.384833445934</v>
+        <v>2621.57</v>
       </c>
       <c r="G30" t="n">
-        <v>4066.940000000001</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9915,20 +9915,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3774</v>
+        <v>4645</v>
       </c>
       <c r="E31" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="F31" t="n">
-        <v>1277.505166554066</v>
+        <v>1572.384833445934</v>
       </c>
       <c r="G31" t="n">
-        <v>3304.24</v>
+        <v>4066.940000000001</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -9943,28 +9943,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>610</v>
+        <v>3774</v>
       </c>
       <c r="E32" t="n">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="F32" t="n">
-        <v>158.09</v>
+        <v>1277.505166554066</v>
       </c>
       <c r="G32" t="n">
-        <v>777.6833333333334</v>
+        <v>3304.24</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -10042,25 +10042,25 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28986</v>
+        <v>610</v>
       </c>
       <c r="E35" t="n">
-        <v>295</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>3183.28</v>
+        <v>158.09</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -10075,28 +10075,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32287</v>
+        <v>28986</v>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="F36" t="n">
-        <v>3614.42</v>
+        <v>3183.28</v>
       </c>
       <c r="G36" t="n">
-        <v>10168.64</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10108,28 +10108,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7950</v>
+        <v>32287</v>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>308</v>
       </c>
       <c r="F37" t="n">
-        <v>1004.78</v>
+        <v>3614.42</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>10168.64</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10150,19 +10150,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8341</v>
+        <v>7950</v>
       </c>
       <c r="E38" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="F38" t="n">
-        <v>1562.07</v>
+        <v>1004.78</v>
       </c>
       <c r="G38" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10183,19 +10183,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9226</v>
+        <v>8341</v>
       </c>
       <c r="E39" t="n">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="F39" t="n">
-        <v>1008.17</v>
+        <v>1562.07</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10216,13 +10216,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8979</v>
+        <v>9226</v>
       </c>
       <c r="E40" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F40" t="n">
-        <v>983.1600000000001</v>
+        <v>1008.17</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -10240,7 +10240,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -10249,19 +10249,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11236</v>
+        <v>8979</v>
       </c>
       <c r="E41" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="F41" t="n">
-        <v>1192.3</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10282,19 +10282,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16717</v>
+        <v>11235</v>
       </c>
       <c r="E42" t="n">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="F42" t="n">
-        <v>960.66</v>
+        <v>1192.3</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10306,28 +10306,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25551</v>
+        <v>16711</v>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="F43" t="n">
-        <v>1055.65</v>
+        <v>960.66</v>
       </c>
       <c r="G43" t="n">
-        <v>9235.59</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -10339,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8043</v>
+        <v>8517</v>
       </c>
       <c r="E44" t="n">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="F44" t="n">
-        <v>993.070229937643</v>
+        <v>351.8833333333334</v>
       </c>
       <c r="G44" t="n">
-        <v>6438.99</v>
+        <v>3078.53</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10372,25 +10372,25 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6350</v>
+        <v>8517</v>
       </c>
       <c r="E45" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="F45" t="n">
-        <v>784.0778976174809</v>
+        <v>351.8833333333334</v>
       </c>
       <c r="G45" t="n">
-        <v>5083.9</v>
+        <v>3078.53</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -10405,7 +10405,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10414,19 +10414,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15503</v>
+        <v>8517</v>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="F46" t="n">
-        <v>1914.251872444876</v>
+        <v>351.8833333333334</v>
       </c>
       <c r="G46" t="n">
-        <v>12411.86</v>
+        <v>3078.53</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10438,28 +10438,28 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>822</v>
+        <v>8042</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F47" t="n">
-        <v>659.9957274352352</v>
+        <v>993.070229937643</v>
       </c>
       <c r="G47" t="n">
-        <v>3420.532190891349</v>
+        <v>6438.99</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10480,19 +10480,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6575</v>
+        <v>6350</v>
       </c>
       <c r="E48" t="n">
-        <v>403</v>
+        <v>86</v>
       </c>
       <c r="F48" t="n">
-        <v>5280.838359111231</v>
+        <v>784.0778976174809</v>
       </c>
       <c r="G48" t="n">
-        <v>27368.77960169272</v>
+        <v>5083.9</v>
       </c>
       <c r="H48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10513,19 +10513,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15211</v>
+        <v>15503</v>
       </c>
       <c r="E49" t="n">
-        <v>932</v>
+        <v>210</v>
       </c>
       <c r="F49" t="n">
-        <v>12217.27132487589</v>
+        <v>1914.251872444876</v>
       </c>
       <c r="G49" t="n">
-        <v>63317.93997210768</v>
+        <v>12411.86</v>
       </c>
       <c r="H49" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -10542,20 +10542,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>466</v>
+        <v>822</v>
       </c>
       <c r="E50" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F50" t="n">
-        <v>373.9014090855015</v>
+        <v>659.9957274352352</v>
       </c>
       <c r="G50" t="n">
-        <v>1937.8031596759</v>
+        <v>3565.030388745155</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -10575,23 +10575,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>55</v>
+        <v>6575</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>403</v>
       </c>
       <c r="F51" t="n">
-        <v>43.79317949214766</v>
+        <v>5280.838359111231</v>
       </c>
       <c r="G51" t="n">
-        <v>226.965075632362</v>
+        <v>28524.95621667498</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -10603,28 +10603,28 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>27</v>
+        <v>15211</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>932</v>
       </c>
       <c r="F52" t="n">
-        <v>9.176666666666668</v>
+        <v>12217.27132487589</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>65992.76590771766</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -10636,28 +10636,28 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>27</v>
+        <v>466</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F53" t="n">
-        <v>9.176666666666668</v>
+        <v>373.9014090855015</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2019.664416562832</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10669,25 +10669,25 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GYS6CJD9</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>9.176666666666668</v>
+        <v>43.79317949214766</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>236.5530702993798</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -10702,28 +10702,28 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1316</v>
+        <v>27</v>
       </c>
       <c r="E55" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>379.16</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G55" t="n">
-        <v>1987.29</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -10735,28 +10735,28 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6745</v>
+        <v>27</v>
       </c>
       <c r="E56" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>429.1377866497453</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G56" t="n">
-        <v>2880.5</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -10768,28 +10768,28 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>19823</v>
+        <v>27</v>
       </c>
       <c r="E57" t="n">
-        <v>118</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>1261.282213350255</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G57" t="n">
-        <v>8466.1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -10801,28 +10801,28 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17292</v>
+        <v>1314</v>
       </c>
       <c r="E58" t="n">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="F58" t="n">
-        <v>1369.61</v>
+        <v>379.16</v>
       </c>
       <c r="G58" t="n">
-        <v>5761.02</v>
+        <v>1987.29</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10834,30 +10834,129 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>6745</v>
+      </c>
+      <c r="E59" t="n">
+        <v>40</v>
+      </c>
+      <c r="F59" t="n">
+        <v>429.1377866497453</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2880.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>19823</v>
+      </c>
+      <c r="E60" t="n">
+        <v>118</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1261.282213350255</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8466.1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>17285</v>
+      </c>
+      <c r="E61" t="n">
+        <v>116</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1369.61</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5761.02</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D62" t="n">
         <v>187</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E62" t="n">
         <v>5</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F62" t="n">
         <v>45.68</v>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9420,23 +9420,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8084</v>
+        <v>14408</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>351.09</v>
+        <v>625.7253013104111</v>
       </c>
       <c r="G16" t="n">
-        <v>4942.653333333333</v>
+        <v>8808.975608171429</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9453,20 +9453,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8084</v>
+        <v>9844</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F17" t="n">
-        <v>351.09</v>
+        <v>427.5446986895889</v>
       </c>
       <c r="G17" t="n">
-        <v>4942.653333333333</v>
+        <v>6018.984391828569</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -9481,28 +9481,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8084</v>
+        <v>14042</v>
       </c>
       <c r="E18" t="n">
-        <v>31</v>
+        <v>247</v>
       </c>
       <c r="F18" t="n">
-        <v>351.09</v>
+        <v>2635.45</v>
       </c>
       <c r="G18" t="n">
-        <v>4942.653333333333</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9523,19 +9523,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14042</v>
+        <v>9644</v>
       </c>
       <c r="E19" t="n">
-        <v>247</v>
+        <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>2635.45</v>
+        <v>1598.452309254072</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5057.64</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9552,23 +9552,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9644</v>
+        <v>3392</v>
       </c>
       <c r="E20" t="n">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="F20" t="n">
-        <v>1598.452309254072</v>
+        <v>562.187690745928</v>
       </c>
       <c r="G20" t="n">
-        <v>5057.64</v>
+        <v>1778.81</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9580,25 +9580,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3392</v>
+        <v>12966</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="F21" t="n">
-        <v>562.187690745928</v>
+        <v>1920.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1778.81</v>
+        <v>2880.5</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -9613,28 +9613,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12966</v>
+        <v>2866</v>
       </c>
       <c r="E22" t="n">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
-        <v>1920.04</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>2880.5</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -9712,28 +9712,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2866</v>
+        <v>4348</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>350.6266666666667</v>
+        <v>1038.49</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>5083.06</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9745,28 +9745,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4348</v>
+        <v>418</v>
       </c>
       <c r="E26" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="F26" t="n">
-        <v>1038.49</v>
+        <v>185.36</v>
       </c>
       <c r="G26" t="n">
-        <v>5083.06</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -9811,28 +9811,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>418</v>
+        <v>4433</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>185.36</v>
+        <v>589.86</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9853,19 +9853,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4433</v>
+        <v>25205</v>
       </c>
       <c r="E29" t="n">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="F29" t="n">
-        <v>589.86</v>
+        <v>2621.57</v>
       </c>
       <c r="G29" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9877,28 +9877,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>25205</v>
+        <v>4645</v>
       </c>
       <c r="E30" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="F30" t="n">
-        <v>2621.57</v>
+        <v>1572.384833445934</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4066.940000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9915,20 +9915,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4645</v>
+        <v>3774</v>
       </c>
       <c r="E31" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F31" t="n">
-        <v>1572.384833445934</v>
+        <v>1277.505166554066</v>
       </c>
       <c r="G31" t="n">
-        <v>4066.940000000001</v>
+        <v>3304.24</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -9943,28 +9943,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3774</v>
+        <v>610</v>
       </c>
       <c r="E32" t="n">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
-        <v>1277.505166554066</v>
+        <v>158.09</v>
       </c>
       <c r="G32" t="n">
-        <v>3304.24</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -10042,25 +10042,25 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>610</v>
+        <v>28986</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>295</v>
       </c>
       <c r="F35" t="n">
-        <v>158.09</v>
+        <v>3183.28</v>
       </c>
       <c r="G35" t="n">
-        <v>777.6833333333334</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -10075,28 +10075,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28986</v>
+        <v>32287</v>
       </c>
       <c r="E36" t="n">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="F36" t="n">
-        <v>3183.28</v>
+        <v>3614.42</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>10168.64</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10108,28 +10108,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>32287</v>
+        <v>7950</v>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>90</v>
       </c>
       <c r="F37" t="n">
-        <v>3614.42</v>
+        <v>1004.78</v>
       </c>
       <c r="G37" t="n">
-        <v>10168.64</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10150,19 +10150,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7950</v>
+        <v>8341</v>
       </c>
       <c r="E38" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F38" t="n">
-        <v>1004.78</v>
+        <v>1562.07</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10183,19 +10183,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8341</v>
+        <v>9226</v>
       </c>
       <c r="E39" t="n">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="F39" t="n">
-        <v>1562.07</v>
+        <v>1008.17</v>
       </c>
       <c r="G39" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10216,13 +10216,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9226</v>
+        <v>8979</v>
       </c>
       <c r="E40" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F40" t="n">
-        <v>1008.17</v>
+        <v>983.1600000000001</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -10240,7 +10240,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -10249,19 +10249,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8979</v>
+        <v>11235</v>
       </c>
       <c r="E41" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="F41" t="n">
-        <v>983.1600000000001</v>
+        <v>1192.3</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10282,19 +10282,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11235</v>
+        <v>16711</v>
       </c>
       <c r="E42" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="F42" t="n">
-        <v>1192.3</v>
+        <v>960.66</v>
       </c>
       <c r="G42" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10306,28 +10306,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16711</v>
+        <v>25551</v>
       </c>
       <c r="E43" t="n">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="F43" t="n">
-        <v>960.66</v>
+        <v>1055.65</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>9235.59</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -10339,28 +10339,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8517</v>
+        <v>8042</v>
       </c>
       <c r="E44" t="n">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F44" t="n">
-        <v>351.8833333333334</v>
+        <v>993.070229937643</v>
       </c>
       <c r="G44" t="n">
-        <v>3078.53</v>
+        <v>6438.99</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -10372,25 +10372,25 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8517</v>
+        <v>6350</v>
       </c>
       <c r="E45" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F45" t="n">
-        <v>351.8833333333334</v>
+        <v>784.0778976174809</v>
       </c>
       <c r="G45" t="n">
-        <v>3078.53</v>
+        <v>5083.9</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -10405,7 +10405,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10414,19 +10414,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8517</v>
+        <v>15503</v>
       </c>
       <c r="E46" t="n">
-        <v>37</v>
+        <v>210</v>
       </c>
       <c r="F46" t="n">
-        <v>351.8833333333334</v>
+        <v>1914.251872444876</v>
       </c>
       <c r="G46" t="n">
-        <v>3078.53</v>
+        <v>12411.86</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -10438,28 +10438,28 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8042</v>
+        <v>822</v>
       </c>
       <c r="E47" t="n">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>993.070229937643</v>
+        <v>659.9957274352352</v>
       </c>
       <c r="G47" t="n">
-        <v>6438.99</v>
+        <v>3565.030388745155</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10480,19 +10480,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6350</v>
+        <v>6575</v>
       </c>
       <c r="E48" t="n">
-        <v>86</v>
+        <v>403</v>
       </c>
       <c r="F48" t="n">
-        <v>784.0778976174809</v>
+        <v>5280.838359111231</v>
       </c>
       <c r="G48" t="n">
-        <v>5083.9</v>
+        <v>28524.95621667498</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10513,19 +10513,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15503</v>
+        <v>15211</v>
       </c>
       <c r="E49" t="n">
-        <v>210</v>
+        <v>932</v>
       </c>
       <c r="F49" t="n">
-        <v>1914.251872444876</v>
+        <v>12217.27132487589</v>
       </c>
       <c r="G49" t="n">
-        <v>12411.86</v>
+        <v>65992.76590771766</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -10542,20 +10542,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>822</v>
+        <v>466</v>
       </c>
       <c r="E50" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F50" t="n">
-        <v>659.9957274352352</v>
+        <v>373.9014090855015</v>
       </c>
       <c r="G50" t="n">
-        <v>3565.030388745155</v>
+        <v>2019.664416562832</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -10575,23 +10575,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GYS6CJD9</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6575</v>
+        <v>55</v>
       </c>
       <c r="E51" t="n">
-        <v>403</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>5280.838359111231</v>
+        <v>43.79317949214766</v>
       </c>
       <c r="G51" t="n">
-        <v>28524.95621667498</v>
+        <v>236.5530702993798</v>
       </c>
       <c r="H51" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -10603,28 +10603,28 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15211</v>
+        <v>27</v>
       </c>
       <c r="E52" t="n">
-        <v>932</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>12217.27132487589</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G52" t="n">
-        <v>65992.76590771766</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -10636,28 +10636,28 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>466</v>
+        <v>27</v>
       </c>
       <c r="E53" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>373.9014090855015</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G53" t="n">
-        <v>2019.664416562832</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10669,25 +10669,25 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>43.79317949214766</v>
+        <v>9.176666666666668</v>
       </c>
       <c r="G54" t="n">
-        <v>236.5530702993798</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -10702,28 +10702,28 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>27</v>
+        <v>1314</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F55" t="n">
-        <v>9.176666666666668</v>
+        <v>379.16</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1987.29</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -10735,28 +10735,28 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>27</v>
+        <v>6745</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F56" t="n">
-        <v>9.176666666666668</v>
+        <v>429.1377866497453</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2880.5</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -10768,28 +10768,28 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27</v>
+        <v>19823</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="F57" t="n">
-        <v>9.176666666666668</v>
+        <v>1261.282213350255</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -10801,28 +10801,28 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1314</v>
+        <v>17285</v>
       </c>
       <c r="E58" t="n">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="F58" t="n">
-        <v>379.16</v>
+        <v>1369.61</v>
       </c>
       <c r="G58" t="n">
-        <v>1987.29</v>
+        <v>5761.02</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -10843,120 +10843,21 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6745</v>
+        <v>187</v>
       </c>
       <c r="E59" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
-        <v>429.1377866497453</v>
+        <v>45.68</v>
       </c>
       <c r="G59" t="n">
-        <v>2880.5</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>19823</v>
-      </c>
-      <c r="E60" t="n">
-        <v>118</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1261.282213350255</v>
-      </c>
-      <c r="G60" t="n">
-        <v>8466.1</v>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>17285</v>
-      </c>
-      <c r="E61" t="n">
-        <v>116</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1369.61</v>
-      </c>
-      <c r="G61" t="n">
-        <v>5761.02</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>187</v>
-      </c>
-      <c r="E62" t="n">
-        <v>5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -2215,7 +2215,7 @@
         <v>418</v>
       </c>
       <c r="F64" t="n">
-        <v>145893</v>
+        <v>145892</v>
       </c>
       <c r="G64" t="n">
         <v>18811.02</v>
@@ -2999,7 +2999,7 @@
         <v>219</v>
       </c>
       <c r="F92" t="n">
-        <v>16569</v>
+        <v>16568</v>
       </c>
       <c r="G92" t="n">
         <v>16691.53</v>
@@ -6331,13 +6331,13 @@
         <v>1163</v>
       </c>
       <c r="F211" t="n">
-        <v>295815</v>
+        <v>295814</v>
       </c>
       <c r="G211" t="n">
         <v>21345.74</v>
       </c>
       <c r="H211" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="212">
@@ -7062,10 +7062,10 @@
         <v>10243</v>
       </c>
       <c r="G237" t="n">
-        <v>10167.8</v>
+        <v>15251.7</v>
       </c>
       <c r="H237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -591,7 +591,7 @@
         <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>18468</v>
+        <v>18467</v>
       </c>
       <c r="G6" t="n">
         <v>10168.64</v>
@@ -871,7 +871,7 @@
         <v>466</v>
       </c>
       <c r="F16" t="n">
-        <v>39606</v>
+        <v>39605</v>
       </c>
       <c r="G16" t="n">
         <v>2880.51</v>
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5342.8</v>
+        <v>5321.77</v>
       </c>
       <c r="E20" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F20" t="n">
-        <v>72111</v>
+        <v>72107</v>
       </c>
       <c r="G20" t="n">
         <v>20420.34</v>
@@ -1739,7 +1739,7 @@
         <v>542</v>
       </c>
       <c r="F47" t="n">
-        <v>54664</v>
+        <v>54663</v>
       </c>
       <c r="G47" t="n">
         <v>6184.75</v>
@@ -3167,7 +3167,7 @@
         <v>1265</v>
       </c>
       <c r="F98" t="n">
-        <v>678704</v>
+        <v>678698</v>
       </c>
       <c r="G98" t="n">
         <v>30503.4</v>
@@ -3195,7 +3195,7 @@
         <v>332</v>
       </c>
       <c r="F99" t="n">
-        <v>77543</v>
+        <v>77542</v>
       </c>
       <c r="G99" t="n">
         <v>15251.7</v>
@@ -6331,7 +6331,7 @@
         <v>1163</v>
       </c>
       <c r="F211" t="n">
-        <v>295814</v>
+        <v>295812</v>
       </c>
       <c r="G211" t="n">
         <v>21345.74</v>
@@ -6443,7 +6443,7 @@
         <v>82</v>
       </c>
       <c r="F215" t="n">
-        <v>5126</v>
+        <v>5125</v>
       </c>
       <c r="G215" t="n">
         <v>4066.94</v>
@@ -6611,7 +6611,7 @@
         <v>1649</v>
       </c>
       <c r="F221" t="n">
-        <v>238786</v>
+        <v>238783</v>
       </c>
       <c r="G221" t="n">
         <v>10166.12</v>
@@ -7227,7 +7227,7 @@
         <v>27</v>
       </c>
       <c r="F243" t="n">
-        <v>6738</v>
+        <v>6737</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25205</v>
+        <v>25204</v>
       </c>
       <c r="E29" t="n">
         <v>200</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28986</v>
+        <v>28985</v>
       </c>
       <c r="E35" t="n">
         <v>295</v>

--- a/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week24.xlsx
@@ -1179,7 +1179,7 @@
         <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>21840</v>
+        <v>21839</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -8899,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8953,28 +8953,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7804</v>
+        <v>14408</v>
       </c>
       <c r="E2" t="n">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>1465.12</v>
+        <v>625.7253013104111</v>
       </c>
       <c r="G2" t="n">
-        <v>2541.53</v>
+        <v>8808.975608171429</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -8986,28 +8986,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4098</v>
+        <v>9844</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>595.2</v>
+        <v>427.5446986895889</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>6018.984391828569</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -9019,22 +9019,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>131</v>
+        <v>2866</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>30.30333333333333</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -9052,22 +9052,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>131</v>
+        <v>2866</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>30.30333333333333</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -9085,22 +9085,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>131</v>
+        <v>2866</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>30.30333333333333</v>
+        <v>350.6266666666667</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -9118,28 +9118,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1569</v>
+        <v>4348</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>248.0633333333334</v>
+        <v>1038.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5083.06</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -9151,25 +9151,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1569</v>
+        <v>610</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>248.0633333333334</v>
+        <v>158.09</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -9184,25 +9184,25 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1569</v>
+        <v>610</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>248.0633333333334</v>
+        <v>158.09</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -9217,25 +9217,25 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>98</v>
+        <v>610</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>127.61</v>
+        <v>158.09</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>777.6833333333334</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -9250,1614 +9250,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>98</v>
+        <v>25550</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="F11" t="n">
-        <v>127.61</v>
+        <v>1055.65</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>9235.59</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>24159</v>
-      </c>
-      <c r="E12" t="n">
-        <v>191</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6082.87</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6184.75</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B0DM6BB3VT</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>63820</v>
-      </c>
-      <c r="E13" t="n">
-        <v>373</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6352.87</v>
-      </c>
-      <c r="G13" t="n">
-        <v>19964.78</v>
-      </c>
-      <c r="H13" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B0D67727VG</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>9090</v>
-      </c>
-      <c r="E14" t="n">
-        <v>109</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1110.916101265823</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4804.064860759494</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B0DKK15YNJ</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>13779</v>
-      </c>
-      <c r="E15" t="n">
-        <v>164</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1684.063898734177</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7282.595139240506</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>14408</v>
-      </c>
-      <c r="E16" t="n">
-        <v>56</v>
-      </c>
-      <c r="F16" t="n">
-        <v>625.7253013104111</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8808.975608171429</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>9844</v>
-      </c>
-      <c r="E17" t="n">
-        <v>38</v>
-      </c>
-      <c r="F17" t="n">
-        <v>427.5446986895889</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6018.984391828569</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>14042</v>
-      </c>
-      <c r="E18" t="n">
-        <v>247</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2635.45</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>9644</v>
-      </c>
-      <c r="E19" t="n">
-        <v>160</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1598.452309254072</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5057.64</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B0DCGHVN81</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3392</v>
-      </c>
-      <c r="E20" t="n">
-        <v>56</v>
-      </c>
-      <c r="F20" t="n">
-        <v>562.187690745928</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1778.81</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12966</v>
-      </c>
-      <c r="E21" t="n">
-        <v>170</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1920.04</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2880.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2866</v>
-      </c>
-      <c r="E22" t="n">
-        <v>31</v>
-      </c>
-      <c r="F22" t="n">
-        <v>350.6266666666667</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B0D672NXC8</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2866</v>
-      </c>
-      <c r="E23" t="n">
-        <v>31</v>
-      </c>
-      <c r="F23" t="n">
-        <v>350.6266666666667</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2866</v>
-      </c>
-      <c r="E24" t="n">
-        <v>31</v>
-      </c>
-      <c r="F24" t="n">
-        <v>350.6266666666667</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>4348</v>
-      </c>
-      <c r="E25" t="n">
-        <v>91</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1038.49</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5083.06</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B0D67727VG</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>418</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13</v>
-      </c>
-      <c r="F26" t="n">
-        <v>185.36</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B0DKK15YNJ</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>418</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13</v>
-      </c>
-      <c r="F27" t="n">
-        <v>185.36</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4433</v>
-      </c>
-      <c r="E28" t="n">
-        <v>59</v>
-      </c>
-      <c r="F28" t="n">
-        <v>589.86</v>
-      </c>
-      <c r="G28" t="n">
-        <v>5083.9</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>25204</v>
-      </c>
-      <c r="E29" t="n">
-        <v>200</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2621.57</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0CDPP45BM</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4645</v>
-      </c>
-      <c r="E30" t="n">
-        <v>110</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1572.384833445934</v>
-      </c>
-      <c r="G30" t="n">
-        <v>4066.940000000001</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>3774</v>
-      </c>
-      <c r="E31" t="n">
-        <v>89</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1277.505166554066</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3304.24</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B0D2LJSQXZ</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>610</v>
-      </c>
-      <c r="E32" t="n">
-        <v>16</v>
-      </c>
-      <c r="F32" t="n">
-        <v>158.09</v>
-      </c>
-      <c r="G32" t="n">
-        <v>777.6833333333334</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>610</v>
-      </c>
-      <c r="E33" t="n">
-        <v>16</v>
-      </c>
-      <c r="F33" t="n">
-        <v>158.09</v>
-      </c>
-      <c r="G33" t="n">
-        <v>777.6833333333334</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>610</v>
-      </c>
-      <c r="E34" t="n">
-        <v>16</v>
-      </c>
-      <c r="F34" t="n">
-        <v>158.09</v>
-      </c>
-      <c r="G34" t="n">
-        <v>777.6833333333334</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>28985</v>
-      </c>
-      <c r="E35" t="n">
-        <v>295</v>
-      </c>
-      <c r="F35" t="n">
-        <v>3183.28</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>B0GN94YDY2</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>32287</v>
-      </c>
-      <c r="E36" t="n">
-        <v>308</v>
-      </c>
-      <c r="F36" t="n">
-        <v>3614.42</v>
-      </c>
-      <c r="G36" t="n">
-        <v>10168.64</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>7950</v>
-      </c>
-      <c r="E37" t="n">
-        <v>90</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1004.78</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>8341</v>
-      </c>
-      <c r="E38" t="n">
-        <v>150</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1562.07</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5083.9</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>9226</v>
-      </c>
-      <c r="E39" t="n">
-        <v>92</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1008.17</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>8979</v>
-      </c>
-      <c r="E40" t="n">
-        <v>88</v>
-      </c>
-      <c r="F40" t="n">
-        <v>983.1600000000001</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11235</v>
-      </c>
-      <c r="E41" t="n">
-        <v>110</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1192.3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>5083.9</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>16711</v>
-      </c>
-      <c r="E42" t="n">
-        <v>72</v>
-      </c>
-      <c r="F42" t="n">
-        <v>960.66</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>B0D672NXC8</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>25551</v>
-      </c>
-      <c r="E43" t="n">
-        <v>112</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1055.65</v>
-      </c>
-      <c r="G43" t="n">
-        <v>9235.59</v>
-      </c>
-      <c r="H43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>B0D2LJSQXZ</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>8042</v>
-      </c>
-      <c r="E44" t="n">
-        <v>109</v>
-      </c>
-      <c r="F44" t="n">
-        <v>993.070229937643</v>
-      </c>
-      <c r="G44" t="n">
-        <v>6438.99</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>6350</v>
-      </c>
-      <c r="E45" t="n">
-        <v>86</v>
-      </c>
-      <c r="F45" t="n">
-        <v>784.0778976174809</v>
-      </c>
-      <c r="G45" t="n">
-        <v>5083.9</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>15503</v>
-      </c>
-      <c r="E46" t="n">
-        <v>210</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1914.251872444876</v>
-      </c>
-      <c r="G46" t="n">
-        <v>12411.86</v>
-      </c>
-      <c r="H46" t="n">
-        <v>4</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>822</v>
-      </c>
-      <c r="E47" t="n">
-        <v>50</v>
-      </c>
-      <c r="F47" t="n">
-        <v>659.9957274352352</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3565.030388745155</v>
-      </c>
-      <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>6575</v>
-      </c>
-      <c r="E48" t="n">
-        <v>403</v>
-      </c>
-      <c r="F48" t="n">
-        <v>5280.838359111231</v>
-      </c>
-      <c r="G48" t="n">
-        <v>28524.95621667498</v>
-      </c>
-      <c r="H48" t="n">
-        <v>9</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>15211</v>
-      </c>
-      <c r="E49" t="n">
-        <v>932</v>
-      </c>
-      <c r="F49" t="n">
-        <v>12217.27132487589</v>
-      </c>
-      <c r="G49" t="n">
-        <v>65992.76590771766</v>
-      </c>
-      <c r="H49" t="n">
-        <v>20</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>B0GLHC8CB3</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>466</v>
-      </c>
-      <c r="E50" t="n">
-        <v>29</v>
-      </c>
-      <c r="F50" t="n">
-        <v>373.9014090855015</v>
-      </c>
-      <c r="G50" t="n">
-        <v>2019.664416562832</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>B0GYS6CJD9</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>55</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3</v>
-      </c>
-      <c r="F51" t="n">
-        <v>43.79317949214766</v>
-      </c>
-      <c r="G51" t="n">
-        <v>236.5530702993798</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>B0CDPP45BM</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>27</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>27</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2</v>
-      </c>
-      <c r="F53" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>27</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2</v>
-      </c>
-      <c r="F54" t="n">
-        <v>9.176666666666668</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1314</v>
-      </c>
-      <c r="E55" t="n">
-        <v>33</v>
-      </c>
-      <c r="F55" t="n">
-        <v>379.16</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1987.29</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>6745</v>
-      </c>
-      <c r="E56" t="n">
-        <v>40</v>
-      </c>
-      <c r="F56" t="n">
-        <v>429.1377866497453</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2880.5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>19823</v>
-      </c>
-      <c r="E57" t="n">
-        <v>118</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1261.282213350255</v>
-      </c>
-      <c r="G57" t="n">
-        <v>8466.1</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>17285</v>
-      </c>
-      <c r="E58" t="n">
-        <v>116</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1369.61</v>
-      </c>
-      <c r="G58" t="n">
-        <v>5761.02</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>187</v>
-      </c>
-      <c r="E59" t="n">
-        <v>5</v>
-      </c>
-      <c r="F59" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>
